--- a/OMOP Analysis/Results/Output_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP.xlsx
@@ -400,25 +400,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2498.57</v>
+        <v>525.8200000000001</v>
       </c>
       <c r="B2">
         <v>2.96</v>
       </c>
       <c r="C2">
-        <v>4724469.53</v>
+        <v>60522</v>
       </c>
       <c r="D2">
-        <v>124620.14</v>
+        <v>1215.11</v>
       </c>
       <c r="E2">
-        <v>2106.16</v>
+        <v>455.99</v>
       </c>
       <c r="F2">
-        <v>1131.64</v>
+        <v>227.99</v>
       </c>
       <c r="G2">
-        <v>4491.14</v>
+        <v>854.14</v>
       </c>
     </row>
   </sheetData>
@@ -470,25 +470,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2492.03</v>
+        <v>510.41</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4724469.53</v>
+        <v>60522</v>
       </c>
       <c r="D2">
-        <v>124459.97</v>
+        <v>1197.5</v>
       </c>
       <c r="E2">
-        <v>2097.93</v>
+        <v>433.4</v>
       </c>
       <c r="F2">
-        <v>1126.94</v>
+        <v>196.01</v>
       </c>
       <c r="G2">
-        <v>4480.56</v>
+        <v>827.29</v>
       </c>
     </row>
   </sheetData>
@@ -498,7 +498,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -545,22 +545,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>37951.73</v>
+        <v>7729.42</v>
       </c>
       <c r="C2">
-        <v>114.98</v>
+        <v>50.35</v>
       </c>
       <c r="D2">
-        <v>2060.65</v>
+        <v>74.17</v>
       </c>
       <c r="E2">
         <v>13.2</v>
       </c>
       <c r="F2">
-        <v>28905.1</v>
+        <v>442.99</v>
       </c>
       <c r="G2">
-        <v>206</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>17172</v>
+        <v>4346</v>
       </c>
       <c r="C3">
-        <v>546.97</v>
+        <v>203.2</v>
       </c>
       <c r="D3">
-        <v>143226.09</v>
+        <v>394.1</v>
       </c>
       <c r="E3">
         <v>26.16</v>
       </c>
       <c r="F3">
-        <v>668263.75</v>
+        <v>1363.8</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -595,22 +595,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>1219</v>
+        <v>424</v>
       </c>
       <c r="C4">
-        <v>57.64</v>
+        <v>85.86</v>
       </c>
       <c r="D4">
-        <v>54.56</v>
+        <v>43.29</v>
       </c>
       <c r="E4">
-        <v>26.16</v>
+        <v>52.31</v>
       </c>
       <c r="F4">
-        <v>179.56</v>
+        <v>130.78</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -620,22 +620,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>2067</v>
+        <v>848</v>
       </c>
       <c r="C5">
-        <v>127.51</v>
+        <v>69.75</v>
       </c>
       <c r="D5">
-        <v>124.61</v>
+        <v>39.38</v>
       </c>
       <c r="E5">
         <v>26.16</v>
       </c>
       <c r="F5">
-        <v>366.17</v>
+        <v>130.78</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>23663.12</v>
+        <v>8564.4</v>
       </c>
       <c r="C6">
-        <v>65.7</v>
+        <v>37.98</v>
       </c>
       <c r="D6">
-        <v>16480.85</v>
+        <v>67.88</v>
       </c>
       <c r="E6">
         <v>15.65</v>
       </c>
       <c r="F6">
-        <v>239969.73</v>
+        <v>480.13</v>
       </c>
       <c r="G6">
-        <v>212</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -670,22 +670,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>435372</v>
+        <v>87066</v>
       </c>
       <c r="C7">
-        <v>233.48</v>
+        <v>117.09</v>
       </c>
       <c r="D7">
-        <v>11982.73</v>
+        <v>222.77</v>
       </c>
       <c r="E7">
         <v>20.73</v>
       </c>
       <c r="F7">
-        <v>408523.5</v>
+        <v>1565.22</v>
       </c>
       <c r="G7">
-        <v>1221</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -695,22 +695,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>190214.69</v>
+        <v>36357.52</v>
       </c>
       <c r="C8">
-        <v>97.59999999999999</v>
+        <v>34.18</v>
       </c>
       <c r="D8">
-        <v>2541.79</v>
+        <v>70.03</v>
       </c>
       <c r="E8">
         <v>9.470000000000001</v>
       </c>
       <c r="F8">
-        <v>51174.07</v>
+        <v>753.16</v>
       </c>
       <c r="G8">
-        <v>1224</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9">
@@ -720,22 +720,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>24392.68</v>
+        <v>5995.08</v>
       </c>
       <c r="C9">
-        <v>98.15000000000001</v>
+        <v>54.37</v>
       </c>
       <c r="D9">
-        <v>1142.52</v>
+        <v>150.29</v>
       </c>
       <c r="E9">
         <v>15.65</v>
       </c>
       <c r="F9">
-        <v>11427.13</v>
+        <v>1082.57</v>
       </c>
       <c r="G9">
-        <v>154</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -767,22 +767,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1161</v>
+        <v>232.2</v>
       </c>
       <c r="C11">
-        <v>142.65</v>
-      </c>
-      <c r="D11">
-        <v>180.06</v>
+        <v>492.06</v>
       </c>
       <c r="E11">
-        <v>57.29</v>
+        <v>492.06</v>
       </c>
       <c r="F11">
         <v>492.06</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -792,22 +789,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>6468</v>
+        <v>1408</v>
       </c>
       <c r="C12">
-        <v>137.9</v>
+        <v>51.44</v>
       </c>
       <c r="D12">
-        <v>14221.62</v>
+        <v>139.86</v>
       </c>
       <c r="E12">
         <v>21.71</v>
       </c>
       <c r="F12">
-        <v>79255</v>
+        <v>576.4</v>
       </c>
       <c r="G12">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -817,22 +814,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>34768</v>
+        <v>4633</v>
       </c>
       <c r="C13">
-        <v>114.47</v>
+        <v>40.92</v>
       </c>
       <c r="D13">
-        <v>5080.82</v>
+        <v>44.06</v>
       </c>
       <c r="E13">
         <v>20.23</v>
       </c>
       <c r="F13">
-        <v>61542.71</v>
+        <v>222.57</v>
       </c>
       <c r="G13">
-        <v>194</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -842,22 +839,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>530</v>
+        <v>106</v>
       </c>
       <c r="C14">
-        <v>59.3</v>
+        <v>41.69</v>
       </c>
       <c r="D14">
-        <v>153.42</v>
+        <v>54.09</v>
       </c>
       <c r="E14">
         <v>26.16</v>
       </c>
       <c r="F14">
-        <v>410.61</v>
+        <v>102.65</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -867,22 +864,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>1484</v>
+        <v>318</v>
       </c>
       <c r="C15">
-        <v>91.54000000000001</v>
+        <v>39.23</v>
       </c>
       <c r="D15">
-        <v>57.64</v>
+        <v>15.1</v>
       </c>
       <c r="E15">
         <v>26.16</v>
       </c>
       <c r="F15">
-        <v>156.93</v>
+        <v>52.31</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -892,22 +889,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>2436</v>
+        <v>252</v>
       </c>
       <c r="C16">
-        <v>41.97</v>
+        <v>35.04</v>
       </c>
       <c r="D16">
-        <v>93.93000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="E16">
         <v>20.73</v>
       </c>
       <c r="F16">
-        <v>477.81</v>
+        <v>199.09</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -917,22 +914,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>14994</v>
+        <v>3234</v>
       </c>
       <c r="C17">
-        <v>165.56</v>
+        <v>48.6</v>
       </c>
       <c r="D17">
-        <v>328.8</v>
+        <v>89.78</v>
       </c>
       <c r="E17">
         <v>20.73</v>
       </c>
       <c r="F17">
-        <v>2056.57</v>
+        <v>560.39</v>
       </c>
       <c r="G17">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -942,22 +939,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>252</v>
+        <v>84</v>
       </c>
       <c r="C18">
-        <v>41.55</v>
+        <v>20.73</v>
       </c>
       <c r="D18">
-        <v>538.35</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>20.73</v>
       </c>
       <c r="F18">
-        <v>1375.5</v>
+        <v>20.73</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -967,22 +964,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>3932.5</v>
+        <v>429</v>
       </c>
       <c r="C19">
-        <v>133.01</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="D19">
-        <v>312.94</v>
+        <v>61.11</v>
       </c>
       <c r="E19">
         <v>35.28</v>
       </c>
       <c r="F19">
-        <v>1238.36</v>
+        <v>141.14</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -992,22 +989,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>12490.11</v>
+        <v>2621.05</v>
       </c>
       <c r="C20">
-        <v>63.48</v>
+        <v>41</v>
       </c>
       <c r="D20">
-        <v>1710.6</v>
+        <v>43.23</v>
       </c>
       <c r="E20">
         <v>13.2</v>
       </c>
       <c r="F20">
-        <v>19270.07</v>
+        <v>211.18</v>
       </c>
       <c r="G20">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -1017,22 +1014,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1395541.19</v>
+        <v>288767.74</v>
       </c>
       <c r="C21">
-        <v>123.57</v>
+        <v>44.13</v>
       </c>
       <c r="D21">
-        <v>7487.94</v>
+        <v>116.68</v>
       </c>
       <c r="E21">
         <v>9.470000000000001</v>
       </c>
       <c r="F21">
-        <v>221293.26</v>
+        <v>3068.11</v>
       </c>
       <c r="G21">
-        <v>7261</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="22">
@@ -1042,22 +1039,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>10416672</v>
+        <v>1776810</v>
       </c>
       <c r="C22">
-        <v>381.42</v>
+        <v>108.91</v>
       </c>
       <c r="D22">
-        <v>19241.33</v>
+        <v>262.22</v>
       </c>
       <c r="E22">
         <v>20.73</v>
       </c>
       <c r="F22">
-        <v>922960.5</v>
+        <v>7723.68</v>
       </c>
       <c r="G22">
-        <v>17403</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="23">
@@ -1067,22 +1064,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1299870</v>
+        <v>154082.5</v>
       </c>
       <c r="C23">
-        <v>326.53</v>
+        <v>194.52</v>
       </c>
       <c r="D23">
-        <v>18059.64</v>
+        <v>553.73</v>
       </c>
       <c r="E23">
         <v>35.28</v>
       </c>
       <c r="F23">
-        <v>592431.12</v>
+        <v>6439.47</v>
       </c>
       <c r="G23">
-        <v>2580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24">
@@ -1092,22 +1089,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>39073</v>
+        <v>5863</v>
       </c>
       <c r="C24">
-        <v>130.36</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="D24">
-        <v>332.02</v>
+        <v>120.4</v>
       </c>
       <c r="E24">
         <v>20.23</v>
       </c>
       <c r="F24">
-        <v>2461.71</v>
+        <v>607</v>
       </c>
       <c r="G24">
-        <v>178</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -1117,22 +1114,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>22008</v>
+        <v>7812</v>
       </c>
       <c r="C25">
-        <v>249.33</v>
+        <v>123.51</v>
       </c>
       <c r="D25">
-        <v>23584.78</v>
+        <v>878.8</v>
       </c>
       <c r="E25">
         <v>20.73</v>
       </c>
       <c r="F25">
-        <v>176522.5</v>
+        <v>5043.5</v>
       </c>
       <c r="G25">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -1142,1163 +1139,1029 @@
         </is>
       </c>
       <c r="B26">
-        <v>20904</v>
+        <v>3120</v>
       </c>
       <c r="C26">
-        <v>47.72</v>
+        <v>32.01</v>
       </c>
       <c r="D26">
-        <v>1080.01</v>
+        <v>50.08</v>
       </c>
       <c r="E26">
         <v>19.25</v>
       </c>
       <c r="F26">
-        <v>14049.75</v>
+        <v>295.78</v>
       </c>
       <c r="G26">
-        <v>284</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dietitian Consultant</t>
+          <t>Dietitian Specialist Practitioner</t>
         </is>
       </c>
       <c r="B27">
-        <v>166</v>
+        <v>39</v>
       </c>
       <c r="C27">
-        <v>27.31</v>
-      </c>
-      <c r="D27">
-        <v>11.82</v>
+        <v>19.25</v>
       </c>
       <c r="E27">
-        <v>20.48</v>
+        <v>19.25</v>
       </c>
       <c r="F27">
-        <v>40.96</v>
+        <v>19.25</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dietitian Specialist Practitioner</t>
+          <t>Enrolled Nurse</t>
         </is>
       </c>
       <c r="B28">
-        <v>78</v>
+        <v>31059.38</v>
       </c>
       <c r="C28">
-        <v>22.61</v>
+        <v>38.07</v>
       </c>
       <c r="D28">
-        <v>5.76</v>
+        <v>50.08</v>
       </c>
       <c r="E28">
-        <v>19.25</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F28">
-        <v>27.39</v>
+        <v>359.98</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enrolled Nurse</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B29">
-        <v>160537.43</v>
+        <v>503160</v>
       </c>
       <c r="C29">
-        <v>121.77</v>
+        <v>69.08</v>
       </c>
       <c r="D29">
-        <v>17232.3</v>
+        <v>221.64</v>
       </c>
       <c r="E29">
-        <v>9.470000000000001</v>
+        <v>20.73</v>
       </c>
       <c r="F29">
-        <v>384958.07</v>
+        <v>6052.2</v>
       </c>
       <c r="G29">
-        <v>817</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B30">
-        <v>2272074</v>
+        <v>12433848</v>
       </c>
       <c r="C30">
-        <v>145.07</v>
+        <v>362.82</v>
       </c>
       <c r="D30">
-        <v>6097.41</v>
+        <v>930.54</v>
       </c>
       <c r="E30">
         <v>20.73</v>
       </c>
       <c r="F30">
-        <v>332871</v>
+        <v>30261</v>
       </c>
       <c r="G30">
-        <v>10055</v>
+        <v>21361</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B31">
-        <v>58754136</v>
+        <v>694766.4</v>
       </c>
       <c r="C31">
-        <v>1613.36</v>
+        <v>85.31</v>
       </c>
       <c r="D31">
-        <v>87467.28999999999</v>
+        <v>554.62</v>
       </c>
       <c r="E31">
-        <v>20.73</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F31">
-        <v>3858277.5</v>
+        <v>13830.83</v>
       </c>
       <c r="G31">
-        <v>23226</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Hospital Practitioner</t>
         </is>
       </c>
       <c r="B32">
-        <v>4089644.6</v>
+        <v>420</v>
       </c>
       <c r="C32">
-        <v>197.82</v>
+        <v>51.82</v>
       </c>
       <c r="D32">
-        <v>13203.84</v>
+        <v>35.9</v>
       </c>
       <c r="E32">
-        <v>9.470000000000001</v>
+        <v>20.73</v>
       </c>
       <c r="F32">
-        <v>670795.2</v>
+        <v>82.91</v>
       </c>
       <c r="G32">
-        <v>13329</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hospital Practitioner</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B33">
-        <v>4074</v>
+        <v>191562</v>
       </c>
       <c r="C33">
-        <v>162.98</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="D33">
-        <v>462.5</v>
+        <v>461.59</v>
       </c>
       <c r="E33">
         <v>20.73</v>
       </c>
       <c r="F33">
-        <v>1647.88</v>
+        <v>10087</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Medical Technical Officer</t>
         </is>
       </c>
       <c r="B34">
-        <v>874230</v>
+        <v>348</v>
       </c>
       <c r="C34">
-        <v>202.75</v>
+        <v>6.23</v>
       </c>
       <c r="D34">
-        <v>9325.6</v>
+        <v>10.44</v>
       </c>
       <c r="E34">
-        <v>20.73</v>
+        <v>2.96</v>
       </c>
       <c r="F34">
-        <v>196696.5</v>
+        <v>52.72</v>
       </c>
       <c r="G34">
-        <v>2665</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Medical Director</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B35">
-        <v>42</v>
+        <v>4602</v>
       </c>
       <c r="C35">
-        <v>77.98999999999999</v>
+        <v>10.46</v>
+      </c>
+      <c r="D35">
+        <v>70.31999999999999</v>
       </c>
       <c r="E35">
-        <v>77.98999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="F35">
-        <v>77.98999999999999</v>
+        <v>1080.75</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Medical Technical Officer</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B36">
-        <v>876</v>
+        <v>95.16</v>
       </c>
       <c r="C36">
-        <v>10.27</v>
+        <v>15.65</v>
       </c>
       <c r="D36">
-        <v>880.58</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>2.96</v>
+        <v>15.65</v>
       </c>
       <c r="F36">
-        <v>6484.5</v>
+        <v>15.65</v>
       </c>
       <c r="G36">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B37">
-        <v>22434</v>
+        <v>4504.24</v>
       </c>
       <c r="C37">
-        <v>23.32</v>
+        <v>93.84</v>
       </c>
       <c r="D37">
-        <v>1807.66</v>
+        <v>215.49</v>
       </c>
       <c r="E37">
-        <v>2.96</v>
+        <v>15.65</v>
       </c>
       <c r="F37">
-        <v>43770.38</v>
+        <v>1008.28</v>
       </c>
       <c r="G37">
-        <v>600</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Multi Therapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B38">
-        <v>602.6799999999999</v>
+        <v>53</v>
       </c>
       <c r="C38">
-        <v>22.78</v>
-      </c>
-      <c r="D38">
-        <v>42.38</v>
+        <v>26.16</v>
       </c>
       <c r="E38">
-        <v>15.65</v>
+        <v>26.16</v>
       </c>
       <c r="F38">
-        <v>163.24</v>
+        <v>26.16</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B39">
-        <v>15511.08</v>
+        <v>58842</v>
       </c>
       <c r="C39">
-        <v>142.32</v>
+        <v>71.97</v>
       </c>
       <c r="D39">
-        <v>643.01</v>
+        <v>202.51</v>
       </c>
       <c r="E39">
-        <v>15.65</v>
+        <v>20.73</v>
       </c>
       <c r="F39">
-        <v>4976.33</v>
+        <v>3191.59</v>
       </c>
       <c r="G39">
-        <v>82</v>
+        <v>449</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Multi Therapist</t>
+          <t>Occupational Therapist</t>
         </is>
       </c>
       <c r="B40">
-        <v>848</v>
+        <v>123</v>
       </c>
       <c r="C40">
-        <v>196.21</v>
+        <v>35.82</v>
       </c>
       <c r="D40">
-        <v>117.7</v>
+        <v>26.89</v>
       </c>
       <c r="E40">
-        <v>78.47</v>
+        <v>20.23</v>
       </c>
       <c r="F40">
-        <v>313.86</v>
+        <v>58.27</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Multi Therapist Specialist Practitioner</t>
+          <t>Optometrist</t>
         </is>
       </c>
       <c r="B41">
-        <v>53</v>
+        <v>394.5</v>
       </c>
       <c r="C41">
-        <v>26.16</v>
+        <v>71.27</v>
+      </c>
+      <c r="D41">
+        <v>13.75</v>
       </c>
       <c r="E41">
-        <v>26.16</v>
+        <v>64.89</v>
       </c>
       <c r="F41">
-        <v>26.16</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B42">
-        <v>297276</v>
+        <v>5035</v>
       </c>
       <c r="C42">
-        <v>211.92</v>
+        <v>350.1</v>
       </c>
       <c r="D42">
-        <v>9664.02</v>
+        <v>1059.97</v>
       </c>
       <c r="E42">
-        <v>20.73</v>
+        <v>78.47</v>
       </c>
       <c r="F42">
-        <v>189131.25</v>
+        <v>3905.44</v>
       </c>
       <c r="G42">
-        <v>869</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nursery Nurse</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B43">
-        <v>153.57</v>
+        <v>10277.28</v>
       </c>
       <c r="C43">
-        <v>12.36</v>
+        <v>50.39</v>
       </c>
       <c r="D43">
-        <v>12.11</v>
+        <v>94.48</v>
       </c>
       <c r="E43">
-        <v>9.470000000000001</v>
+        <v>15.65</v>
       </c>
       <c r="F43">
-        <v>41.91</v>
+        <v>571.36</v>
       </c>
       <c r="G43">
-        <v>7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Occupational Therapist</t>
+          <t>Other Community Health Service - Social Care Worker</t>
         </is>
       </c>
       <c r="B44">
-        <v>656</v>
+        <v>88</v>
       </c>
       <c r="C44">
-        <v>83.04000000000001</v>
-      </c>
-      <c r="D44">
-        <v>821.88</v>
+        <v>104.28</v>
       </c>
       <c r="E44">
-        <v>40.47</v>
+        <v>104.28</v>
       </c>
       <c r="F44">
-        <v>2110.04</v>
+        <v>104.28</v>
       </c>
       <c r="G44">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Optometrist</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B45">
-        <v>2630</v>
+        <v>4935</v>
       </c>
       <c r="C45">
-        <v>267.95</v>
+        <v>25.19</v>
       </c>
       <c r="D45">
-        <v>499.52</v>
+        <v>266.59</v>
       </c>
       <c r="E45">
-        <v>64.89</v>
+        <v>11.6</v>
       </c>
       <c r="F45">
-        <v>1544.77</v>
+        <v>2821.96</v>
       </c>
       <c r="G45">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Paramedic Consultant</t>
         </is>
       </c>
       <c r="B46">
-        <v>19875</v>
+        <v>257.5</v>
       </c>
       <c r="C46">
-        <v>767.58</v>
+        <v>27.77</v>
       </c>
       <c r="D46">
-        <v>3372.65</v>
+        <v>29.7</v>
       </c>
       <c r="E46">
-        <v>26.16</v>
+        <v>12.71</v>
       </c>
       <c r="F46">
-        <v>10164.75</v>
+        <v>80.66</v>
       </c>
       <c r="G46">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B47">
-        <v>36129.08</v>
+        <v>5529</v>
       </c>
       <c r="C47">
-        <v>100.57</v>
+        <v>30.78</v>
       </c>
       <c r="D47">
-        <v>2405.63</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="E47">
-        <v>15.65</v>
+        <v>14.06</v>
       </c>
       <c r="F47">
-        <v>34281.39</v>
+        <v>364.08</v>
       </c>
       <c r="G47">
-        <v>224</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Social Care Worker</t>
+          <t>Patient Welfare Officer</t>
         </is>
       </c>
       <c r="B48">
-        <v>748</v>
+        <v>44</v>
       </c>
       <c r="C48">
-        <v>431.15</v>
-      </c>
-      <c r="D48">
-        <v>411.42</v>
+        <v>21.71</v>
       </c>
       <c r="E48">
-        <v>148.14</v>
+        <v>21.71</v>
       </c>
       <c r="F48">
-        <v>729.98</v>
+        <v>21.71</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B49">
-        <v>15228</v>
+        <v>20377</v>
       </c>
       <c r="C49">
-        <v>35.4</v>
+        <v>63.04</v>
       </c>
       <c r="D49">
-        <v>2449.24</v>
+        <v>57.25</v>
       </c>
       <c r="E49">
-        <v>11.6</v>
+        <v>20.23</v>
       </c>
       <c r="F49">
-        <v>33863.5</v>
+        <v>323.73</v>
       </c>
       <c r="G49">
-        <v>271</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Paramedic Consultant</t>
+          <t>Physiotherapist Consultant</t>
         </is>
       </c>
       <c r="B50">
-        <v>695.25</v>
+        <v>1144</v>
       </c>
       <c r="C50">
-        <v>35.52</v>
+        <v>51.81</v>
       </c>
       <c r="D50">
-        <v>88.93000000000001</v>
+        <v>24.02</v>
       </c>
       <c r="E50">
-        <v>12.71</v>
+        <v>35.28</v>
       </c>
       <c r="F50">
-        <v>331.3</v>
+        <v>105.85</v>
       </c>
       <c r="G50">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Physiotherapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B51">
-        <v>17727</v>
+        <v>1537</v>
       </c>
       <c r="C51">
-        <v>48.18</v>
+        <v>55.08</v>
       </c>
       <c r="D51">
-        <v>2180.09</v>
+        <v>33.48</v>
       </c>
       <c r="E51">
-        <v>14.06</v>
+        <v>26.16</v>
       </c>
       <c r="F51">
-        <v>30801.38</v>
+        <v>130.78</v>
       </c>
       <c r="G51">
-        <v>236</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Patient Welfare Officer</t>
+          <t>Practitioner</t>
         </is>
       </c>
       <c r="B52">
-        <v>1584</v>
+        <v>6365.41</v>
       </c>
       <c r="C52">
-        <v>159.89</v>
+        <v>43.65</v>
       </c>
       <c r="D52">
-        <v>738.49</v>
+        <v>62.1</v>
       </c>
       <c r="E52">
-        <v>43.43</v>
+        <v>13.2</v>
       </c>
       <c r="F52">
-        <v>2377.65</v>
+        <v>370.58</v>
       </c>
       <c r="G52">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Pre-reg Pharmacist</t>
         </is>
       </c>
       <c r="B53">
-        <v>97006</v>
+        <v>6</v>
       </c>
       <c r="C53">
-        <v>93.98</v>
-      </c>
-      <c r="D53">
-        <v>14992.62</v>
+        <v>5.27</v>
       </c>
       <c r="E53">
-        <v>20.23</v>
+        <v>5.27</v>
       </c>
       <c r="F53">
-        <v>369256.25</v>
+        <v>5.27</v>
       </c>
       <c r="G53">
-        <v>629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Physiotherapist Consultant</t>
+          <t>Psychotherapist</t>
         </is>
       </c>
       <c r="B54">
-        <v>4218.5</v>
+        <v>643.5</v>
       </c>
       <c r="C54">
-        <v>74.14</v>
+        <v>105.85</v>
       </c>
       <c r="D54">
-        <v>601.24</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E54">
         <v>35.28</v>
       </c>
       <c r="F54">
-        <v>2927.03</v>
+        <v>176.42</v>
       </c>
       <c r="G54">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Physiotherapist Specialist Practitioner</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="B55">
-        <v>5777</v>
+        <v>540.5</v>
       </c>
       <c r="C55">
-        <v>80.43000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="D55">
-        <v>544.8099999999999</v>
+        <v>17.62</v>
       </c>
       <c r="E55">
-        <v>26.16</v>
+        <v>5.8</v>
       </c>
       <c r="F55">
-        <v>3471.5</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="G55">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Practitioner</t>
+          <t>Regional Dental Officer</t>
         </is>
       </c>
       <c r="B56">
-        <v>40465.8</v>
+        <v>1443</v>
       </c>
       <c r="C56">
-        <v>115.91</v>
+        <v>250.28</v>
       </c>
       <c r="D56">
-        <v>3444.18</v>
+        <v>224.08</v>
       </c>
       <c r="E56">
-        <v>13.2</v>
+        <v>64.81</v>
       </c>
       <c r="F56">
-        <v>46970.79</v>
+        <v>493</v>
       </c>
       <c r="G56">
-        <v>227</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pre-reg Pharmacist</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B57">
-        <v>6</v>
+        <v>1111278</v>
       </c>
       <c r="C57">
-        <v>5.27</v>
+        <v>133.07</v>
+      </c>
+      <c r="D57">
+        <v>481.43</v>
       </c>
       <c r="E57">
-        <v>5.27</v>
+        <v>20.73</v>
       </c>
       <c r="F57">
-        <v>5.27</v>
+        <v>15130.5</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>4934</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Psychotherapist</t>
+          <t>Senior House Officer</t>
         </is>
       </c>
       <c r="B58">
-        <v>5791.5</v>
+        <v>1218</v>
       </c>
       <c r="C58">
-        <v>250.89</v>
+        <v>65.02</v>
       </c>
       <c r="D58">
-        <v>6896.6</v>
+        <v>94.03</v>
       </c>
       <c r="E58">
-        <v>35.28</v>
+        <v>20.73</v>
       </c>
       <c r="F58">
-        <v>25757.88</v>
+        <v>378.26</v>
       </c>
       <c r="G58">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Radiologist</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B59">
-        <v>2585</v>
+        <v>508158</v>
       </c>
       <c r="C59">
-        <v>60.49</v>
+        <v>89.2</v>
       </c>
       <c r="D59">
-        <v>240.88</v>
+        <v>719.3099999999999</v>
       </c>
       <c r="E59">
-        <v>5.8</v>
+        <v>20.73</v>
       </c>
       <c r="F59">
-        <v>1209.41</v>
+        <v>30261</v>
       </c>
       <c r="G59">
-        <v>26</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Regional Dental Officer</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B60">
-        <v>4329</v>
+        <v>105252</v>
       </c>
       <c r="C60">
-        <v>394.82</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D60">
-        <v>440.81</v>
+        <v>186.38</v>
       </c>
       <c r="E60">
-        <v>54.78</v>
+        <v>20.73</v>
       </c>
       <c r="F60">
-        <v>1258.69</v>
+        <v>2176.3</v>
       </c>
       <c r="G60">
-        <v>6</v>
+        <v>704</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B61">
-        <v>4654230</v>
+        <v>308</v>
       </c>
       <c r="C61">
-        <v>357.91</v>
+        <v>159.42</v>
       </c>
       <c r="D61">
-        <v>18060.9</v>
+        <v>91.39</v>
       </c>
       <c r="E61">
-        <v>20.73</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F61">
-        <v>635481</v>
+        <v>200.65</v>
       </c>
       <c r="G61">
-        <v>8276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior House Officer</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B62">
-        <v>6216</v>
+        <v>316184.22</v>
       </c>
       <c r="C62">
-        <v>117.87</v>
+        <v>53.16</v>
       </c>
       <c r="D62">
-        <v>639.9400000000001</v>
+        <v>134.9</v>
       </c>
       <c r="E62">
-        <v>20.73</v>
+        <v>13.2</v>
       </c>
       <c r="F62">
-        <v>3026.1</v>
+        <v>4817.52</v>
       </c>
       <c r="G62">
-        <v>39</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B63">
-        <v>2366532</v>
+        <v>4377.36</v>
       </c>
       <c r="C63">
-        <v>212.93</v>
+        <v>58.53</v>
       </c>
       <c r="D63">
-        <v>17026.35</v>
+        <v>50.23</v>
       </c>
       <c r="E63">
-        <v>20.73</v>
+        <v>15.65</v>
       </c>
       <c r="F63">
-        <v>877569</v>
+        <v>240.57</v>
       </c>
       <c r="G63">
-        <v>7107</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Specialist Registrar</t>
         </is>
       </c>
       <c r="B64">
-        <v>534408</v>
+        <v>42</v>
       </c>
       <c r="C64">
-        <v>267.87</v>
-      </c>
-      <c r="D64">
-        <v>27850.36</v>
+        <v>48.97</v>
       </c>
       <c r="E64">
-        <v>20.73</v>
+        <v>48.97</v>
       </c>
       <c r="F64">
-        <v>847308</v>
+        <v>48.97</v>
       </c>
       <c r="G64">
-        <v>1274</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Social Care Support Worker</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B65">
-        <v>176</v>
+        <v>281484</v>
       </c>
       <c r="C65">
-        <v>209.95</v>
+        <v>88.69</v>
       </c>
       <c r="D65">
-        <v>11096.64</v>
+        <v>243.68</v>
       </c>
       <c r="E65">
-        <v>157.98</v>
+        <v>20.73</v>
       </c>
       <c r="F65">
-        <v>15851</v>
+        <v>6052.2</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B66">
-        <v>660</v>
+        <v>1802</v>
       </c>
       <c r="C66">
-        <v>130.71</v>
+        <v>156.16</v>
       </c>
       <c r="D66">
-        <v>221.22</v>
+        <v>281.77</v>
       </c>
       <c r="E66">
-        <v>21.71</v>
+        <v>75.77</v>
       </c>
       <c r="F66">
-        <v>499.81</v>
+        <v>1018.31</v>
       </c>
       <c r="G66">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Trainee Practitioner</t>
         </is>
       </c>
       <c r="B67">
-        <v>1552998.87</v>
+        <v>902.22</v>
       </c>
       <c r="C67">
-        <v>142.55</v>
+        <v>22.83</v>
       </c>
       <c r="D67">
-        <v>7087.99</v>
+        <v>1436.94</v>
       </c>
       <c r="E67">
-        <v>13.2</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F67">
-        <v>370948.78</v>
+        <v>6915.41</v>
       </c>
       <c r="G67">
-        <v>6928</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>21950.24</v>
-      </c>
-      <c r="C68">
-        <v>173.52</v>
-      </c>
-      <c r="D68">
-        <v>676.28</v>
-      </c>
-      <c r="E68">
-        <v>15.65</v>
-      </c>
-      <c r="F68">
-        <v>5332.66</v>
-      </c>
-      <c r="G68">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Specialist Registrar</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>756</v>
-      </c>
-      <c r="C69">
-        <v>80.39</v>
-      </c>
-      <c r="D69">
-        <v>4977.96</v>
-      </c>
-      <c r="E69">
-        <v>20.73</v>
-      </c>
-      <c r="F69">
-        <v>15130.5</v>
-      </c>
-      <c r="G69">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>1468656</v>
-      </c>
-      <c r="C70">
-        <v>276.39</v>
-      </c>
-      <c r="D70">
-        <v>16983.73</v>
-      </c>
-      <c r="E70">
-        <v>20.73</v>
-      </c>
-      <c r="F70">
-        <v>877569</v>
-      </c>
-      <c r="G70">
-        <v>3377</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>7102</v>
-      </c>
-      <c r="C71">
-        <v>285.77</v>
-      </c>
-      <c r="D71">
-        <v>1010.47</v>
-      </c>
-      <c r="E71">
-        <v>26.16</v>
-      </c>
-      <c r="F71">
-        <v>3440.23</v>
-      </c>
-      <c r="G71">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Trainee Practitioner</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>3954.41</v>
-      </c>
-      <c r="C72">
-        <v>33.79</v>
-      </c>
-      <c r="D72">
-        <v>2378.99</v>
-      </c>
-      <c r="E72">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="F72">
-        <v>20746.24</v>
-      </c>
-      <c r="G72">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2308,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2355,22 +2218,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>37951.73</v>
+        <v>7729.42</v>
       </c>
       <c r="C2">
-        <v>114.98</v>
+        <v>50.35</v>
       </c>
       <c r="D2">
-        <v>2060.65</v>
+        <v>74.17</v>
       </c>
       <c r="E2">
         <v>13.2</v>
       </c>
       <c r="F2">
-        <v>28905.1</v>
+        <v>442.99</v>
       </c>
       <c r="G2">
-        <v>206</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -2380,22 +2243,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>17172</v>
+        <v>4346</v>
       </c>
       <c r="C3">
-        <v>546.97</v>
+        <v>203.2</v>
       </c>
       <c r="D3">
-        <v>143226.09</v>
+        <v>394.1</v>
       </c>
       <c r="E3">
         <v>26.16</v>
       </c>
       <c r="F3">
-        <v>668263.75</v>
+        <v>1363.8</v>
       </c>
       <c r="G3">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2405,22 +2268,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>1219</v>
+        <v>424</v>
       </c>
       <c r="C4">
-        <v>57.64</v>
+        <v>85.86</v>
       </c>
       <c r="D4">
-        <v>54.56</v>
+        <v>43.29</v>
       </c>
       <c r="E4">
-        <v>26.16</v>
+        <v>52.31</v>
       </c>
       <c r="F4">
-        <v>179.56</v>
+        <v>130.78</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2430,22 +2293,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>2067</v>
+        <v>848</v>
       </c>
       <c r="C5">
-        <v>127.51</v>
+        <v>69.75</v>
       </c>
       <c r="D5">
-        <v>124.61</v>
+        <v>39.38</v>
       </c>
       <c r="E5">
         <v>26.16</v>
       </c>
       <c r="F5">
-        <v>366.17</v>
+        <v>130.78</v>
       </c>
       <c r="G5">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2455,22 +2318,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>23663.12</v>
+        <v>8564.4</v>
       </c>
       <c r="C6">
-        <v>65.7</v>
+        <v>37.98</v>
       </c>
       <c r="D6">
-        <v>16480.85</v>
+        <v>67.88</v>
       </c>
       <c r="E6">
         <v>15.65</v>
       </c>
       <c r="F6">
-        <v>239969.73</v>
+        <v>480.13</v>
       </c>
       <c r="G6">
-        <v>212</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7">
@@ -2480,22 +2343,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>435372</v>
+        <v>87066</v>
       </c>
       <c r="C7">
-        <v>233.48</v>
+        <v>117.09</v>
       </c>
       <c r="D7">
-        <v>11982.73</v>
+        <v>222.77</v>
       </c>
       <c r="E7">
         <v>20.73</v>
       </c>
       <c r="F7">
-        <v>408523.5</v>
+        <v>1565.22</v>
       </c>
       <c r="G7">
-        <v>1221</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -2505,22 +2368,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>190214.69</v>
+        <v>36357.52</v>
       </c>
       <c r="C8">
-        <v>97.59999999999999</v>
+        <v>34.18</v>
       </c>
       <c r="D8">
-        <v>2541.79</v>
+        <v>70.03</v>
       </c>
       <c r="E8">
         <v>9.470000000000001</v>
       </c>
       <c r="F8">
-        <v>51174.07</v>
+        <v>753.16</v>
       </c>
       <c r="G8">
-        <v>1224</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9">
@@ -2530,22 +2393,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>24392.68</v>
+        <v>5995.08</v>
       </c>
       <c r="C9">
-        <v>98.15000000000001</v>
+        <v>54.37</v>
       </c>
       <c r="D9">
-        <v>1142.52</v>
+        <v>150.29</v>
       </c>
       <c r="E9">
         <v>15.65</v>
       </c>
       <c r="F9">
-        <v>11427.13</v>
+        <v>1082.57</v>
       </c>
       <c r="G9">
-        <v>154</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -2577,22 +2440,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1161</v>
+        <v>232.2</v>
       </c>
       <c r="C11">
-        <v>142.65</v>
-      </c>
-      <c r="D11">
-        <v>180.06</v>
+        <v>492.06</v>
       </c>
       <c r="E11">
-        <v>57.29</v>
+        <v>492.06</v>
       </c>
       <c r="F11">
         <v>492.06</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -2602,22 +2462,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>6468</v>
+        <v>1408</v>
       </c>
       <c r="C12">
-        <v>137.9</v>
+        <v>51.44</v>
       </c>
       <c r="D12">
-        <v>14221.62</v>
+        <v>139.86</v>
       </c>
       <c r="E12">
         <v>21.71</v>
       </c>
       <c r="F12">
-        <v>79255</v>
+        <v>576.4</v>
       </c>
       <c r="G12">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -2627,22 +2487,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>34768</v>
+        <v>4633</v>
       </c>
       <c r="C13">
-        <v>114.47</v>
+        <v>40.92</v>
       </c>
       <c r="D13">
-        <v>5080.82</v>
+        <v>44.06</v>
       </c>
       <c r="E13">
         <v>20.23</v>
       </c>
       <c r="F13">
-        <v>61542.71</v>
+        <v>222.57</v>
       </c>
       <c r="G13">
-        <v>194</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2652,22 +2512,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>530</v>
+        <v>106</v>
       </c>
       <c r="C14">
-        <v>59.3</v>
+        <v>41.69</v>
       </c>
       <c r="D14">
-        <v>153.42</v>
+        <v>54.09</v>
       </c>
       <c r="E14">
         <v>26.16</v>
       </c>
       <c r="F14">
-        <v>410.61</v>
+        <v>102.65</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2677,22 +2537,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>1484</v>
+        <v>318</v>
       </c>
       <c r="C15">
-        <v>91.54000000000001</v>
+        <v>39.23</v>
       </c>
       <c r="D15">
-        <v>57.64</v>
+        <v>15.1</v>
       </c>
       <c r="E15">
         <v>26.16</v>
       </c>
       <c r="F15">
-        <v>156.93</v>
+        <v>52.31</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -2702,22 +2562,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>2436</v>
+        <v>252</v>
       </c>
       <c r="C16">
-        <v>41.97</v>
+        <v>35.04</v>
       </c>
       <c r="D16">
-        <v>93.93000000000001</v>
+        <v>78.23</v>
       </c>
       <c r="E16">
         <v>20.73</v>
       </c>
       <c r="F16">
-        <v>477.81</v>
+        <v>199.09</v>
       </c>
       <c r="G16">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -2727,22 +2587,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>14994</v>
+        <v>3234</v>
       </c>
       <c r="C17">
-        <v>165.56</v>
+        <v>48.6</v>
       </c>
       <c r="D17">
-        <v>328.8</v>
+        <v>89.78</v>
       </c>
       <c r="E17">
         <v>20.73</v>
       </c>
       <c r="F17">
-        <v>2056.57</v>
+        <v>560.39</v>
       </c>
       <c r="G17">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -2752,22 +2612,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>252</v>
+        <v>84</v>
       </c>
       <c r="C18">
-        <v>41.55</v>
+        <v>20.73</v>
       </c>
       <c r="D18">
-        <v>538.35</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>20.73</v>
       </c>
       <c r="F18">
-        <v>1375.5</v>
+        <v>20.73</v>
       </c>
       <c r="G18">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2777,22 +2637,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>3932.5</v>
+        <v>429</v>
       </c>
       <c r="C19">
-        <v>133.01</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="D19">
-        <v>312.94</v>
+        <v>61.11</v>
       </c>
       <c r="E19">
         <v>35.28</v>
       </c>
       <c r="F19">
-        <v>1238.36</v>
+        <v>141.14</v>
       </c>
       <c r="G19">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2802,22 +2662,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>12490.11</v>
+        <v>2621.05</v>
       </c>
       <c r="C20">
-        <v>63.48</v>
+        <v>41</v>
       </c>
       <c r="D20">
-        <v>1710.6</v>
+        <v>43.23</v>
       </c>
       <c r="E20">
         <v>13.2</v>
       </c>
       <c r="F20">
-        <v>19270.07</v>
+        <v>211.18</v>
       </c>
       <c r="G20">
-        <v>128</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -2827,22 +2687,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1395541.19</v>
+        <v>288767.74</v>
       </c>
       <c r="C21">
-        <v>123.57</v>
+        <v>44.13</v>
       </c>
       <c r="D21">
-        <v>7487.94</v>
+        <v>116.68</v>
       </c>
       <c r="E21">
         <v>9.470000000000001</v>
       </c>
       <c r="F21">
-        <v>221293.26</v>
+        <v>3068.11</v>
       </c>
       <c r="G21">
-        <v>7261</v>
+        <v>3748</v>
       </c>
     </row>
     <row r="22">
@@ -2852,22 +2712,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>10416672</v>
+        <v>1776810</v>
       </c>
       <c r="C22">
-        <v>381.42</v>
+        <v>108.91</v>
       </c>
       <c r="D22">
-        <v>19241.33</v>
+        <v>262.22</v>
       </c>
       <c r="E22">
         <v>20.73</v>
       </c>
       <c r="F22">
-        <v>922960.5</v>
+        <v>7723.68</v>
       </c>
       <c r="G22">
-        <v>17403</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="23">
@@ -2877,22 +2737,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>1299870</v>
+        <v>154082.5</v>
       </c>
       <c r="C23">
-        <v>326.53</v>
+        <v>194.52</v>
       </c>
       <c r="D23">
-        <v>18059.64</v>
+        <v>553.73</v>
       </c>
       <c r="E23">
         <v>35.28</v>
       </c>
       <c r="F23">
-        <v>592431.12</v>
+        <v>6439.47</v>
       </c>
       <c r="G23">
-        <v>2580</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24">
@@ -2902,22 +2762,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>39073</v>
+        <v>5863</v>
       </c>
       <c r="C24">
-        <v>130.36</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="D24">
-        <v>332.02</v>
+        <v>120.4</v>
       </c>
       <c r="E24">
         <v>20.23</v>
       </c>
       <c r="F24">
-        <v>2461.71</v>
+        <v>607</v>
       </c>
       <c r="G24">
-        <v>178</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -2927,22 +2787,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>22008</v>
+        <v>7812</v>
       </c>
       <c r="C25">
-        <v>249.33</v>
+        <v>123.51</v>
       </c>
       <c r="D25">
-        <v>23584.78</v>
+        <v>878.8</v>
       </c>
       <c r="E25">
         <v>20.73</v>
       </c>
       <c r="F25">
-        <v>176522.5</v>
+        <v>5043.5</v>
       </c>
       <c r="G25">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -2952,1188 +2812,1054 @@
         </is>
       </c>
       <c r="B26">
-        <v>20904</v>
+        <v>3120</v>
       </c>
       <c r="C26">
-        <v>47.72</v>
+        <v>32.01</v>
       </c>
       <c r="D26">
-        <v>1080.01</v>
+        <v>50.08</v>
       </c>
       <c r="E26">
         <v>19.25</v>
       </c>
       <c r="F26">
-        <v>14049.75</v>
+        <v>295.78</v>
       </c>
       <c r="G26">
-        <v>284</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dietitian Consultant</t>
+          <t>Dietitian Specialist Practitioner</t>
         </is>
       </c>
       <c r="B27">
-        <v>166</v>
+        <v>39</v>
       </c>
       <c r="C27">
-        <v>27.31</v>
-      </c>
-      <c r="D27">
-        <v>11.82</v>
+        <v>19.25</v>
       </c>
       <c r="E27">
-        <v>20.48</v>
+        <v>19.25</v>
       </c>
       <c r="F27">
-        <v>40.96</v>
+        <v>19.25</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dietitian Specialist Practitioner</t>
+          <t>Enrolled Nurse</t>
         </is>
       </c>
       <c r="B28">
-        <v>78</v>
+        <v>31059.38</v>
       </c>
       <c r="C28">
-        <v>22.61</v>
+        <v>38.07</v>
       </c>
       <c r="D28">
-        <v>5.76</v>
+        <v>50.08</v>
       </c>
       <c r="E28">
-        <v>19.25</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F28">
-        <v>27.39</v>
+        <v>359.98</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>442</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Enrolled Nurse</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B29">
-        <v>160537.43</v>
+        <v>503160</v>
       </c>
       <c r="C29">
-        <v>121.77</v>
+        <v>69.08</v>
       </c>
       <c r="D29">
-        <v>17232.3</v>
+        <v>221.64</v>
       </c>
       <c r="E29">
-        <v>9.470000000000001</v>
+        <v>20.73</v>
       </c>
       <c r="F29">
-        <v>384958.07</v>
+        <v>6052.2</v>
       </c>
       <c r="G29">
-        <v>817</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B30">
-        <v>2272074</v>
+        <v>12433848</v>
       </c>
       <c r="C30">
-        <v>145.07</v>
+        <v>362.82</v>
       </c>
       <c r="D30">
-        <v>6097.41</v>
+        <v>930.54</v>
       </c>
       <c r="E30">
         <v>20.73</v>
       </c>
       <c r="F30">
-        <v>332871</v>
+        <v>30261</v>
       </c>
       <c r="G30">
-        <v>10055</v>
+        <v>21361</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B31">
-        <v>58754136</v>
+        <v>694766.4</v>
       </c>
       <c r="C31">
-        <v>1613.36</v>
+        <v>85.31</v>
       </c>
       <c r="D31">
-        <v>87467.28999999999</v>
+        <v>554.62</v>
       </c>
       <c r="E31">
-        <v>20.73</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F31">
-        <v>3858277.5</v>
+        <v>13830.83</v>
       </c>
       <c r="G31">
-        <v>23226</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Hospital Practitioner</t>
         </is>
       </c>
       <c r="B32">
-        <v>4089644.6</v>
+        <v>420</v>
       </c>
       <c r="C32">
-        <v>197.82</v>
+        <v>51.82</v>
       </c>
       <c r="D32">
-        <v>13203.84</v>
+        <v>35.9</v>
       </c>
       <c r="E32">
-        <v>9.470000000000001</v>
+        <v>20.73</v>
       </c>
       <c r="F32">
-        <v>670795.2</v>
+        <v>82.91</v>
       </c>
       <c r="G32">
-        <v>13329</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hospital Practitioner</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B33">
-        <v>4074</v>
+        <v>191562</v>
       </c>
       <c r="C33">
-        <v>162.98</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="D33">
-        <v>462.5</v>
+        <v>461.59</v>
       </c>
       <c r="E33">
         <v>20.73</v>
       </c>
       <c r="F33">
-        <v>1647.88</v>
+        <v>10087</v>
       </c>
       <c r="G33">
-        <v>18</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Medical Technical Officer</t>
         </is>
       </c>
       <c r="B34">
-        <v>874230</v>
+        <v>348</v>
       </c>
       <c r="C34">
-        <v>202.75</v>
+        <v>6.23</v>
       </c>
       <c r="D34">
-        <v>9325.6</v>
+        <v>10.44</v>
       </c>
       <c r="E34">
-        <v>20.73</v>
+        <v>2.96</v>
       </c>
       <c r="F34">
-        <v>196696.5</v>
+        <v>52.72</v>
       </c>
       <c r="G34">
-        <v>2665</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Medical Director</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B35">
-        <v>42</v>
+        <v>4602</v>
       </c>
       <c r="C35">
-        <v>77.98999999999999</v>
+        <v>10.46</v>
+      </c>
+      <c r="D35">
+        <v>70.31999999999999</v>
       </c>
       <c r="E35">
-        <v>77.98999999999999</v>
+        <v>2.96</v>
       </c>
       <c r="F35">
-        <v>77.98999999999999</v>
+        <v>1080.75</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Medical Technical Officer</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B36">
-        <v>876</v>
+        <v>95.16</v>
       </c>
       <c r="C36">
-        <v>10.27</v>
+        <v>15.65</v>
       </c>
       <c r="D36">
-        <v>880.58</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>2.96</v>
+        <v>15.65</v>
       </c>
       <c r="F36">
-        <v>6484.5</v>
+        <v>15.65</v>
       </c>
       <c r="G36">
-        <v>54</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B37">
-        <v>22434</v>
+        <v>4504.24</v>
       </c>
       <c r="C37">
-        <v>23.32</v>
+        <v>93.84</v>
       </c>
       <c r="D37">
-        <v>1807.66</v>
+        <v>215.49</v>
       </c>
       <c r="E37">
-        <v>2.96</v>
+        <v>15.65</v>
       </c>
       <c r="F37">
-        <v>43770.38</v>
+        <v>1008.28</v>
       </c>
       <c r="G37">
-        <v>600</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Multi Therapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B38">
-        <v>602.6799999999999</v>
+        <v>53</v>
       </c>
       <c r="C38">
-        <v>22.78</v>
-      </c>
-      <c r="D38">
-        <v>42.38</v>
+        <v>26.16</v>
       </c>
       <c r="E38">
-        <v>15.65</v>
+        <v>26.16</v>
       </c>
       <c r="F38">
-        <v>163.24</v>
+        <v>26.16</v>
       </c>
       <c r="G38">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B39">
-        <v>15511.08</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>142.32</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>643.01</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>15.65</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>4976.33</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>82</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Multi Therapist</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B40">
-        <v>848</v>
+        <v>58842</v>
       </c>
       <c r="C40">
-        <v>196.21</v>
+        <v>71.97</v>
       </c>
       <c r="D40">
-        <v>117.7</v>
+        <v>202.51</v>
       </c>
       <c r="E40">
-        <v>78.47</v>
+        <v>20.73</v>
       </c>
       <c r="F40">
-        <v>313.86</v>
+        <v>3191.59</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Multi Therapist Specialist Practitioner</t>
+          <t>Occupational Therapist</t>
         </is>
       </c>
       <c r="B41">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="C41">
-        <v>26.16</v>
+        <v>35.82</v>
+      </c>
+      <c r="D41">
+        <v>26.89</v>
       </c>
       <c r="E41">
-        <v>26.16</v>
+        <v>20.23</v>
       </c>
       <c r="F41">
-        <v>26.16</v>
+        <v>58.27</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>Optometrist</t>
         </is>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>394.5</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>71.27</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>64.89</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="G42">
-        <v>61</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B43">
-        <v>297276</v>
+        <v>5035</v>
       </c>
       <c r="C43">
-        <v>211.92</v>
+        <v>350.1</v>
       </c>
       <c r="D43">
-        <v>9664.02</v>
+        <v>1059.97</v>
       </c>
       <c r="E43">
-        <v>20.73</v>
+        <v>78.47</v>
       </c>
       <c r="F43">
-        <v>189131.25</v>
+        <v>3905.44</v>
       </c>
       <c r="G43">
-        <v>869</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nursery Nurse</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B44">
-        <v>153.57</v>
+        <v>10277.28</v>
       </c>
       <c r="C44">
-        <v>12.36</v>
+        <v>50.39</v>
       </c>
       <c r="D44">
-        <v>12.11</v>
+        <v>94.48</v>
       </c>
       <c r="E44">
-        <v>9.470000000000001</v>
+        <v>15.65</v>
       </c>
       <c r="F44">
-        <v>41.91</v>
+        <v>571.36</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Occupational Therapist</t>
+          <t>Other Community Health Service - Social Care Worker</t>
         </is>
       </c>
       <c r="B45">
-        <v>656</v>
+        <v>88</v>
       </c>
       <c r="C45">
-        <v>83.04000000000001</v>
-      </c>
-      <c r="D45">
-        <v>821.88</v>
+        <v>104.28</v>
       </c>
       <c r="E45">
-        <v>40.47</v>
+        <v>104.28</v>
       </c>
       <c r="F45">
-        <v>2110.04</v>
+        <v>104.28</v>
       </c>
       <c r="G45">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Optometrist</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B46">
-        <v>2630</v>
+        <v>4935</v>
       </c>
       <c r="C46">
-        <v>267.95</v>
+        <v>25.19</v>
       </c>
       <c r="D46">
-        <v>499.52</v>
+        <v>266.59</v>
       </c>
       <c r="E46">
-        <v>64.89</v>
+        <v>11.6</v>
       </c>
       <c r="F46">
-        <v>1544.77</v>
+        <v>2821.96</v>
       </c>
       <c r="G46">
-        <v>8</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Paramedic Consultant</t>
         </is>
       </c>
       <c r="B47">
-        <v>19875</v>
+        <v>257.5</v>
       </c>
       <c r="C47">
-        <v>767.58</v>
+        <v>27.77</v>
       </c>
       <c r="D47">
-        <v>3372.65</v>
+        <v>29.7</v>
       </c>
       <c r="E47">
-        <v>26.16</v>
+        <v>12.71</v>
       </c>
       <c r="F47">
-        <v>10164.75</v>
+        <v>80.66</v>
       </c>
       <c r="G47">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B48">
-        <v>36129.08</v>
+        <v>5529</v>
       </c>
       <c r="C48">
-        <v>100.57</v>
+        <v>30.78</v>
       </c>
       <c r="D48">
-        <v>2405.63</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="E48">
-        <v>15.65</v>
+        <v>14.06</v>
       </c>
       <c r="F48">
-        <v>34281.39</v>
+        <v>364.08</v>
       </c>
       <c r="G48">
-        <v>224</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Social Care Worker</t>
+          <t>Patient Welfare Officer</t>
         </is>
       </c>
       <c r="B49">
-        <v>748</v>
+        <v>44</v>
       </c>
       <c r="C49">
-        <v>431.15</v>
-      </c>
-      <c r="D49">
-        <v>411.42</v>
+        <v>21.71</v>
       </c>
       <c r="E49">
-        <v>148.14</v>
+        <v>21.71</v>
       </c>
       <c r="F49">
-        <v>729.98</v>
+        <v>21.71</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B50">
-        <v>15228</v>
+        <v>20377</v>
       </c>
       <c r="C50">
-        <v>35.4</v>
+        <v>63.04</v>
       </c>
       <c r="D50">
-        <v>2449.24</v>
+        <v>57.25</v>
       </c>
       <c r="E50">
-        <v>11.6</v>
+        <v>20.23</v>
       </c>
       <c r="F50">
-        <v>33863.5</v>
+        <v>323.73</v>
       </c>
       <c r="G50">
-        <v>271</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Paramedic Consultant</t>
+          <t>Physiotherapist Consultant</t>
         </is>
       </c>
       <c r="B51">
-        <v>695.25</v>
+        <v>1144</v>
       </c>
       <c r="C51">
-        <v>35.52</v>
+        <v>51.81</v>
       </c>
       <c r="D51">
-        <v>88.93000000000001</v>
+        <v>24.02</v>
       </c>
       <c r="E51">
-        <v>12.71</v>
+        <v>35.28</v>
       </c>
       <c r="F51">
-        <v>331.3</v>
+        <v>105.85</v>
       </c>
       <c r="G51">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Physiotherapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B52">
-        <v>17727</v>
+        <v>1537</v>
       </c>
       <c r="C52">
-        <v>48.18</v>
+        <v>55.08</v>
       </c>
       <c r="D52">
-        <v>2180.09</v>
+        <v>33.48</v>
       </c>
       <c r="E52">
-        <v>14.06</v>
+        <v>26.16</v>
       </c>
       <c r="F52">
-        <v>30801.38</v>
+        <v>130.78</v>
       </c>
       <c r="G52">
-        <v>236</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Patient Welfare Officer</t>
+          <t>Practitioner</t>
         </is>
       </c>
       <c r="B53">
-        <v>1584</v>
+        <v>6365.41</v>
       </c>
       <c r="C53">
-        <v>159.89</v>
+        <v>43.65</v>
       </c>
       <c r="D53">
-        <v>738.49</v>
+        <v>62.1</v>
       </c>
       <c r="E53">
-        <v>43.43</v>
+        <v>13.2</v>
       </c>
       <c r="F53">
-        <v>2377.65</v>
+        <v>370.58</v>
       </c>
       <c r="G53">
-        <v>9</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Pre-reg Pharmacist</t>
         </is>
       </c>
       <c r="B54">
-        <v>97006</v>
+        <v>6</v>
       </c>
       <c r="C54">
-        <v>93.98</v>
-      </c>
-      <c r="D54">
-        <v>14992.62</v>
+        <v>5.27</v>
       </c>
       <c r="E54">
-        <v>20.23</v>
+        <v>5.27</v>
       </c>
       <c r="F54">
-        <v>369256.25</v>
+        <v>5.27</v>
       </c>
       <c r="G54">
-        <v>629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Physiotherapist Consultant</t>
+          <t>Psychotherapist</t>
         </is>
       </c>
       <c r="B55">
-        <v>4218.5</v>
+        <v>643.5</v>
       </c>
       <c r="C55">
-        <v>74.14</v>
+        <v>105.85</v>
       </c>
       <c r="D55">
-        <v>601.24</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E55">
         <v>35.28</v>
       </c>
       <c r="F55">
-        <v>2927.03</v>
+        <v>176.42</v>
       </c>
       <c r="G55">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Physiotherapist Specialist Practitioner</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="B56">
-        <v>5777</v>
+        <v>540.5</v>
       </c>
       <c r="C56">
-        <v>80.43000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="D56">
-        <v>544.8099999999999</v>
+        <v>17.62</v>
       </c>
       <c r="E56">
-        <v>26.16</v>
+        <v>5.8</v>
       </c>
       <c r="F56">
-        <v>3471.5</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="G56">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Practitioner</t>
+          <t>Regional Dental Officer</t>
         </is>
       </c>
       <c r="B57">
-        <v>40465.8</v>
+        <v>1443</v>
       </c>
       <c r="C57">
-        <v>115.91</v>
+        <v>250.28</v>
       </c>
       <c r="D57">
-        <v>3444.18</v>
+        <v>224.08</v>
       </c>
       <c r="E57">
-        <v>13.2</v>
+        <v>64.81</v>
       </c>
       <c r="F57">
-        <v>46970.79</v>
+        <v>493</v>
       </c>
       <c r="G57">
-        <v>227</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pre-reg Pharmacist</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B58">
-        <v>6</v>
+        <v>1111278</v>
       </c>
       <c r="C58">
-        <v>5.27</v>
+        <v>133.07</v>
+      </c>
+      <c r="D58">
+        <v>481.43</v>
       </c>
       <c r="E58">
-        <v>5.27</v>
+        <v>20.73</v>
       </c>
       <c r="F58">
-        <v>5.27</v>
+        <v>15130.5</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>4934</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Psychotherapist</t>
+          <t>Senior House Officer</t>
         </is>
       </c>
       <c r="B59">
-        <v>5791.5</v>
+        <v>1218</v>
       </c>
       <c r="C59">
-        <v>250.89</v>
+        <v>65.02</v>
       </c>
       <c r="D59">
-        <v>6896.6</v>
+        <v>94.03</v>
       </c>
       <c r="E59">
-        <v>35.28</v>
+        <v>20.73</v>
       </c>
       <c r="F59">
-        <v>25757.88</v>
+        <v>378.26</v>
       </c>
       <c r="G59">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Radiologist</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B60">
-        <v>2585</v>
+        <v>508158</v>
       </c>
       <c r="C60">
-        <v>60.49</v>
+        <v>89.2</v>
       </c>
       <c r="D60">
-        <v>240.88</v>
+        <v>719.3099999999999</v>
       </c>
       <c r="E60">
-        <v>5.8</v>
+        <v>20.73</v>
       </c>
       <c r="F60">
-        <v>1209.41</v>
+        <v>30261</v>
       </c>
       <c r="G60">
-        <v>26</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Regional Dental Officer</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B61">
-        <v>4329</v>
+        <v>105252</v>
       </c>
       <c r="C61">
-        <v>394.82</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D61">
-        <v>440.81</v>
+        <v>186.38</v>
       </c>
       <c r="E61">
-        <v>54.78</v>
+        <v>20.73</v>
       </c>
       <c r="F61">
-        <v>1258.69</v>
+        <v>2176.3</v>
       </c>
       <c r="G61">
-        <v>6</v>
+        <v>704</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B62">
-        <v>4654230</v>
+        <v>308</v>
       </c>
       <c r="C62">
-        <v>357.91</v>
+        <v>159.42</v>
       </c>
       <c r="D62">
-        <v>18060.9</v>
+        <v>91.39</v>
       </c>
       <c r="E62">
-        <v>20.73</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F62">
-        <v>635481</v>
+        <v>200.65</v>
       </c>
       <c r="G62">
-        <v>8276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior House Officer</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B63">
-        <v>6216</v>
+        <v>316184.22</v>
       </c>
       <c r="C63">
-        <v>117.87</v>
+        <v>53.16</v>
       </c>
       <c r="D63">
-        <v>639.9400000000001</v>
+        <v>134.9</v>
       </c>
       <c r="E63">
-        <v>20.73</v>
+        <v>13.2</v>
       </c>
       <c r="F63">
-        <v>3026.1</v>
+        <v>4817.52</v>
       </c>
       <c r="G63">
-        <v>39</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B64">
-        <v>2366532</v>
+        <v>4377.36</v>
       </c>
       <c r="C64">
-        <v>212.93</v>
+        <v>58.53</v>
       </c>
       <c r="D64">
-        <v>17026.35</v>
+        <v>50.23</v>
       </c>
       <c r="E64">
-        <v>20.73</v>
+        <v>15.65</v>
       </c>
       <c r="F64">
-        <v>877569</v>
+        <v>240.57</v>
       </c>
       <c r="G64">
-        <v>7107</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Specialist Registrar</t>
         </is>
       </c>
       <c r="B65">
-        <v>534408</v>
+        <v>42</v>
       </c>
       <c r="C65">
-        <v>267.87</v>
-      </c>
-      <c r="D65">
-        <v>27850.36</v>
+        <v>48.97</v>
       </c>
       <c r="E65">
-        <v>20.73</v>
+        <v>48.97</v>
       </c>
       <c r="F65">
-        <v>847308</v>
+        <v>48.97</v>
       </c>
       <c r="G65">
-        <v>1274</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Social Care Support Worker</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B66">
-        <v>176</v>
+        <v>281484</v>
       </c>
       <c r="C66">
-        <v>209.95</v>
+        <v>88.69</v>
       </c>
       <c r="D66">
-        <v>11096.64</v>
+        <v>243.68</v>
       </c>
       <c r="E66">
-        <v>157.98</v>
+        <v>20.73</v>
       </c>
       <c r="F66">
-        <v>15851</v>
+        <v>6052.2</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B67">
-        <v>660</v>
+        <v>1802</v>
       </c>
       <c r="C67">
-        <v>130.71</v>
+        <v>156.16</v>
       </c>
       <c r="D67">
-        <v>221.22</v>
+        <v>281.77</v>
       </c>
       <c r="E67">
-        <v>21.71</v>
+        <v>75.77</v>
       </c>
       <c r="F67">
-        <v>499.81</v>
+        <v>1018.31</v>
       </c>
       <c r="G67">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Trainee Practitioner</t>
         </is>
       </c>
       <c r="B68">
-        <v>1552998.87</v>
+        <v>902.22</v>
       </c>
       <c r="C68">
-        <v>142.55</v>
+        <v>22.83</v>
       </c>
       <c r="D68">
-        <v>7087.99</v>
+        <v>1436.94</v>
       </c>
       <c r="E68">
-        <v>13.2</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F68">
-        <v>370948.78</v>
+        <v>6915.41</v>
       </c>
       <c r="G68">
-        <v>6928</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>21950.24</v>
-      </c>
-      <c r="C69">
-        <v>173.52</v>
-      </c>
-      <c r="D69">
-        <v>676.28</v>
-      </c>
-      <c r="E69">
-        <v>15.65</v>
-      </c>
-      <c r="F69">
-        <v>5332.66</v>
-      </c>
-      <c r="G69">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Specialist Registrar</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>756</v>
-      </c>
-      <c r="C70">
-        <v>80.39</v>
-      </c>
-      <c r="D70">
-        <v>4977.96</v>
-      </c>
-      <c r="E70">
-        <v>20.73</v>
-      </c>
-      <c r="F70">
-        <v>15130.5</v>
-      </c>
-      <c r="G70">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>1468656</v>
-      </c>
-      <c r="C71">
-        <v>276.39</v>
-      </c>
-      <c r="D71">
-        <v>16983.73</v>
-      </c>
-      <c r="E71">
-        <v>20.73</v>
-      </c>
-      <c r="F71">
-        <v>877569</v>
-      </c>
-      <c r="G71">
-        <v>3377</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>7102</v>
-      </c>
-      <c r="C72">
-        <v>285.77</v>
-      </c>
-      <c r="D72">
-        <v>1010.47</v>
-      </c>
-      <c r="E72">
-        <v>26.16</v>
-      </c>
-      <c r="F72">
-        <v>3440.23</v>
-      </c>
-      <c r="G72">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Trainee Practitioner</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>3954.41</v>
-      </c>
-      <c r="C73">
-        <v>33.79</v>
-      </c>
-      <c r="D73">
-        <v>2378.99</v>
-      </c>
-      <c r="E73">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="F73">
-        <v>20746.24</v>
-      </c>
-      <c r="G73">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -4185,25 +3911,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2499.03</v>
+        <v>525.64</v>
       </c>
       <c r="B2">
         <v>2.96</v>
       </c>
       <c r="C2">
-        <v>4740899.7</v>
+        <v>60522</v>
       </c>
       <c r="D2">
-        <v>124642.14</v>
+        <v>1213.79</v>
       </c>
       <c r="E2">
-        <v>2103.44</v>
+        <v>455.99</v>
       </c>
       <c r="F2">
-        <v>1132.85</v>
+        <v>227.99</v>
       </c>
       <c r="G2">
-        <v>4493.64</v>
+        <v>853.9400000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4255,25 +3981,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2492.49</v>
+        <v>510.24</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>4740899.7</v>
+        <v>60522</v>
       </c>
       <c r="D2">
-        <v>124481.95</v>
+        <v>1196.21</v>
       </c>
       <c r="E2">
-        <v>2096.32</v>
+        <v>433.48</v>
       </c>
       <c r="F2">
-        <v>1126.94</v>
+        <v>196.01</v>
       </c>
       <c r="G2">
-        <v>4481.73</v>
+        <v>827.29</v>
       </c>
     </row>
   </sheetData>
@@ -4330,22 +4056,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>79773246</v>
+        <v>16611882</v>
       </c>
       <c r="C2">
-        <v>2183.71</v>
+        <v>471.18</v>
       </c>
       <c r="D2">
-        <v>108823.43</v>
+        <v>1129.26</v>
       </c>
       <c r="E2">
         <v>20.73</v>
       </c>
       <c r="F2">
-        <v>3979321.5</v>
+        <v>60522</v>
       </c>
       <c r="G2">
-        <v>23300</v>
+        <v>22086</v>
       </c>
     </row>
     <row r="3">
@@ -4355,22 +4081,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>5607514.18</v>
+        <v>1121252.7</v>
       </c>
       <c r="C3">
-        <v>230.19</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D3">
-        <v>15334.78</v>
+        <v>180.79</v>
       </c>
       <c r="E3">
         <v>9.470000000000001</v>
       </c>
       <c r="F3">
-        <v>907830</v>
+        <v>6052.2</v>
       </c>
       <c r="G3">
-        <v>15531</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="4">
@@ -4380,22 +4106,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>6006572.63</v>
+        <v>974708.28</v>
       </c>
       <c r="C4">
-        <v>244.29</v>
+        <v>91.55</v>
       </c>
       <c r="D4">
-        <v>17845.99</v>
+        <v>560.0599999999999</v>
       </c>
       <c r="E4">
         <v>2.96</v>
       </c>
       <c r="F4">
-        <v>1011942.25</v>
+        <v>20746.24</v>
       </c>
       <c r="G4">
-        <v>15757</v>
+        <v>6434</v>
       </c>
     </row>
   </sheetData>
@@ -4452,22 +4178,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>79773246</v>
+        <v>16611882</v>
       </c>
       <c r="C2">
-        <v>2183.71</v>
+        <v>471.18</v>
       </c>
       <c r="D2">
-        <v>108823.43</v>
+        <v>1129.26</v>
       </c>
       <c r="E2">
         <v>20.73</v>
       </c>
       <c r="F2">
-        <v>3979321.5</v>
+        <v>60522</v>
       </c>
       <c r="G2">
-        <v>23300</v>
+        <v>22086</v>
       </c>
     </row>
     <row r="3">
@@ -4492,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>61</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="4">
@@ -4502,22 +4228,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>5607514.18</v>
+        <v>1121252.7</v>
       </c>
       <c r="C4">
-        <v>230.19</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="D4">
-        <v>15334.78</v>
+        <v>180.79</v>
       </c>
       <c r="E4">
         <v>9.470000000000001</v>
       </c>
       <c r="F4">
-        <v>907830</v>
+        <v>6052.2</v>
       </c>
       <c r="G4">
-        <v>15531</v>
+        <v>9212</v>
       </c>
     </row>
     <row r="5">
@@ -4527,22 +4253,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>6006572.63</v>
+        <v>974708.28</v>
       </c>
       <c r="C5">
-        <v>244.29</v>
+        <v>91.55</v>
       </c>
       <c r="D5">
-        <v>17845.99</v>
+        <v>560.0599999999999</v>
       </c>
       <c r="E5">
         <v>2.96</v>
       </c>
       <c r="F5">
-        <v>1011942.25</v>
+        <v>20746.24</v>
       </c>
       <c r="G5">
-        <v>15757</v>
+        <v>6434</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP.xlsx
@@ -398,7 +398,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>549.86</v>
+        <v>591.46</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -407,16 +407,16 @@
         <v>9915.709999999999</v>
       </c>
       <c r="D2">
-        <v>669.72</v>
+        <v>711.65</v>
       </c>
       <c r="E2">
-        <v>457.61</v>
+        <v>498.07</v>
       </c>
       <c r="F2">
-        <v>227.17</v>
+        <v>249.06</v>
       </c>
       <c r="G2">
-        <v>852.25</v>
+        <v>923.27</v>
       </c>
     </row>
   </sheetData>
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -764,325 +764,350 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>39851.22</v>
+        <v>1616796.5</v>
       </c>
       <c r="C11">
-        <v>35.51</v>
+        <v>114.07</v>
       </c>
       <c r="D11">
-        <v>70.56999999999999</v>
+        <v>236.17</v>
       </c>
       <c r="E11">
-        <v>9.6</v>
+        <v>21.01</v>
       </c>
       <c r="F11">
-        <v>763.62</v>
+        <v>3443.79</v>
       </c>
       <c r="G11">
-        <v>643</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B12">
-        <v>11171.5</v>
+        <v>39851.22</v>
       </c>
       <c r="C12">
-        <v>28.3</v>
+        <v>35.51</v>
       </c>
       <c r="D12">
-        <v>59.24</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E12">
-        <v>11.76</v>
+        <v>9.6</v>
       </c>
       <c r="F12">
-        <v>440.17</v>
+        <v>763.62</v>
       </c>
       <c r="G12">
-        <v>231</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B13">
-        <v>38898</v>
+        <v>11231.5</v>
       </c>
       <c r="C13">
-        <v>19.44</v>
+        <v>28.45</v>
       </c>
       <c r="D13">
-        <v>41.16</v>
+        <v>62.84</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>11.76</v>
       </c>
       <c r="F13">
-        <v>483.93</v>
+        <v>533.83</v>
       </c>
       <c r="G13">
-        <v>1182</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B14">
-        <v>21484</v>
+        <v>38898</v>
       </c>
       <c r="C14">
-        <v>61.55</v>
+        <v>19.44</v>
       </c>
       <c r="D14">
-        <v>57.02</v>
+        <v>41.16</v>
       </c>
       <c r="E14">
-        <v>20.51</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>328.22</v>
+        <v>483.93</v>
       </c>
       <c r="G14">
-        <v>192</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B15">
-        <v>1262352</v>
+        <v>21484</v>
       </c>
       <c r="C15">
-        <v>89.12</v>
+        <v>61.55</v>
       </c>
       <c r="D15">
-        <v>150.42</v>
+        <v>57.02</v>
       </c>
       <c r="E15">
-        <v>21.01</v>
+        <v>20.51</v>
       </c>
       <c r="F15">
-        <v>3334.89</v>
+        <v>328.22</v>
       </c>
       <c r="G15">
-        <v>8078</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B16">
-        <v>4756</v>
+        <v>1262352</v>
       </c>
       <c r="C16">
-        <v>41.38</v>
+        <v>89.12</v>
       </c>
       <c r="D16">
-        <v>44.02</v>
+        <v>150.42</v>
       </c>
       <c r="E16">
-        <v>20.51</v>
+        <v>21.01</v>
       </c>
       <c r="F16">
-        <v>225.65</v>
+        <v>3334.89</v>
       </c>
       <c r="G16">
-        <v>63</v>
+        <v>8078</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B17">
-        <v>6642</v>
+        <v>4756</v>
       </c>
       <c r="C17">
-        <v>110.43</v>
+        <v>41.38</v>
       </c>
       <c r="D17">
-        <v>130.24</v>
+        <v>44.02</v>
       </c>
       <c r="E17">
         <v>20.51</v>
       </c>
       <c r="F17">
-        <v>615.42</v>
+        <v>225.65</v>
       </c>
       <c r="G17">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B18">
-        <v>307330.42</v>
+        <v>6642</v>
       </c>
       <c r="C18">
-        <v>45.1</v>
+        <v>110.43</v>
       </c>
       <c r="D18">
-        <v>106.1</v>
+        <v>130.24</v>
       </c>
       <c r="E18">
-        <v>9.6</v>
+        <v>20.51</v>
       </c>
       <c r="F18">
-        <v>3110.69</v>
+        <v>615.42</v>
       </c>
       <c r="G18">
-        <v>3943</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B19">
-        <v>3198</v>
+        <v>307330.42</v>
       </c>
       <c r="C19">
-        <v>31.93</v>
+        <v>45.1</v>
       </c>
       <c r="D19">
-        <v>50.02</v>
+        <v>106.1</v>
       </c>
       <c r="E19">
-        <v>19.51</v>
+        <v>9.6</v>
       </c>
       <c r="F19">
-        <v>299.89</v>
+        <v>3110.69</v>
       </c>
       <c r="G19">
-        <v>57</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B20">
-        <v>145506.84</v>
+        <v>3198</v>
       </c>
       <c r="C20">
-        <v>70.53</v>
+        <v>31.93</v>
       </c>
       <c r="D20">
-        <v>156.78</v>
+        <v>50.02</v>
       </c>
       <c r="E20">
-        <v>15.87</v>
+        <v>19.51</v>
       </c>
       <c r="F20">
-        <v>3235.89</v>
+        <v>299.89</v>
       </c>
       <c r="G20">
-        <v>1155</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B21">
-        <v>416262</v>
+        <v>146195.6</v>
       </c>
       <c r="C21">
-        <v>91.31999999999999</v>
+        <v>70.87</v>
       </c>
       <c r="D21">
-        <v>165.5</v>
+        <v>141.5</v>
       </c>
       <c r="E21">
-        <v>21.01</v>
+        <v>15.87</v>
       </c>
       <c r="F21">
-        <v>2629.8</v>
+        <v>2443.86</v>
       </c>
       <c r="G21">
-        <v>2591</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>308</v>
+        <v>416262</v>
       </c>
       <c r="C22">
-        <v>155.17</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="D22">
-        <v>84.36</v>
+        <v>165.5</v>
       </c>
       <c r="E22">
-        <v>72.39</v>
+        <v>21.01</v>
       </c>
       <c r="F22">
-        <v>191.7</v>
+        <v>2629.8</v>
       </c>
       <c r="G22">
-        <v>2</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>308</v>
+      </c>
+      <c r="C23">
+        <v>155.17</v>
+      </c>
+      <c r="D23">
+        <v>84.36</v>
+      </c>
+      <c r="E23">
+        <v>72.39</v>
+      </c>
+      <c r="F23">
+        <v>191.7</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B23">
-        <v>18864.37</v>
-      </c>
-      <c r="C23">
-        <v>53.82</v>
-      </c>
-      <c r="D23">
-        <v>93.31</v>
-      </c>
-      <c r="E23">
+      <c r="B24">
+        <v>19142.95</v>
+      </c>
+      <c r="C24">
+        <v>54.61</v>
+      </c>
+      <c r="D24">
+        <v>102.27</v>
+      </c>
+      <c r="E24">
         <v>13.38</v>
       </c>
-      <c r="F23">
-        <v>925.46</v>
-      </c>
-      <c r="G23">
+      <c r="F24">
+        <v>1097.6</v>
+      </c>
+      <c r="G24">
         <v>198</v>
       </c>
     </row>
@@ -1093,7 +1118,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1361,350 +1386,375 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>1616796.5</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>114.07</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>236.17</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>21.01</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3443.79</v>
       </c>
       <c r="G11">
-        <v>723</v>
+        <v>8334</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B12">
-        <v>39851.22</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>35.51</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>70.56999999999999</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>763.62</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>643</v>
+        <v>631</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B13">
-        <v>11171.5</v>
+        <v>39851.22</v>
       </c>
       <c r="C13">
-        <v>28.3</v>
+        <v>35.51</v>
       </c>
       <c r="D13">
-        <v>59.24</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="E13">
-        <v>11.76</v>
+        <v>9.6</v>
       </c>
       <c r="F13">
-        <v>440.17</v>
+        <v>763.62</v>
       </c>
       <c r="G13">
-        <v>231</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B14">
-        <v>38898</v>
+        <v>11231.5</v>
       </c>
       <c r="C14">
-        <v>19.44</v>
+        <v>28.45</v>
       </c>
       <c r="D14">
-        <v>41.16</v>
+        <v>62.84</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>11.76</v>
       </c>
       <c r="F14">
-        <v>483.93</v>
+        <v>533.83</v>
       </c>
       <c r="G14">
-        <v>1182</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>21484</v>
+        <v>38898</v>
       </c>
       <c r="C15">
-        <v>61.55</v>
+        <v>19.44</v>
       </c>
       <c r="D15">
-        <v>57.02</v>
+        <v>41.16</v>
       </c>
       <c r="E15">
-        <v>20.51</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>328.22</v>
+        <v>483.93</v>
       </c>
       <c r="G15">
-        <v>192</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B16">
-        <v>1262352</v>
+        <v>21484</v>
       </c>
       <c r="C16">
-        <v>89.12</v>
+        <v>61.55</v>
       </c>
       <c r="D16">
-        <v>150.42</v>
+        <v>57.02</v>
       </c>
       <c r="E16">
-        <v>21.01</v>
+        <v>20.51</v>
       </c>
       <c r="F16">
-        <v>3334.89</v>
+        <v>328.22</v>
       </c>
       <c r="G16">
-        <v>8078</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B17">
-        <v>4756</v>
+        <v>1262352</v>
       </c>
       <c r="C17">
-        <v>41.38</v>
+        <v>89.12</v>
       </c>
       <c r="D17">
-        <v>44.02</v>
+        <v>150.42</v>
       </c>
       <c r="E17">
-        <v>20.51</v>
+        <v>21.01</v>
       </c>
       <c r="F17">
-        <v>225.65</v>
+        <v>3334.89</v>
       </c>
       <c r="G17">
-        <v>63</v>
+        <v>8078</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B18">
-        <v>6642</v>
+        <v>4756</v>
       </c>
       <c r="C18">
-        <v>110.43</v>
+        <v>41.38</v>
       </c>
       <c r="D18">
-        <v>130.24</v>
+        <v>44.02</v>
       </c>
       <c r="E18">
         <v>20.51</v>
       </c>
       <c r="F18">
-        <v>615.42</v>
+        <v>225.65</v>
       </c>
       <c r="G18">
-        <v>32</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B19">
-        <v>307330.42</v>
+        <v>6642</v>
       </c>
       <c r="C19">
-        <v>45.1</v>
+        <v>110.43</v>
       </c>
       <c r="D19">
-        <v>106.1</v>
+        <v>130.24</v>
       </c>
       <c r="E19">
-        <v>9.6</v>
+        <v>20.51</v>
       </c>
       <c r="F19">
-        <v>3110.69</v>
+        <v>615.42</v>
       </c>
       <c r="G19">
-        <v>3943</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B20">
-        <v>3198</v>
+        <v>307330.42</v>
       </c>
       <c r="C20">
-        <v>31.93</v>
+        <v>45.1</v>
       </c>
       <c r="D20">
-        <v>50.02</v>
+        <v>106.1</v>
       </c>
       <c r="E20">
-        <v>19.51</v>
+        <v>9.6</v>
       </c>
       <c r="F20">
-        <v>299.89</v>
+        <v>3110.69</v>
       </c>
       <c r="G20">
-        <v>57</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B21">
-        <v>145506.84</v>
+        <v>3198</v>
       </c>
       <c r="C21">
-        <v>70.53</v>
+        <v>31.93</v>
       </c>
       <c r="D21">
-        <v>156.78</v>
+        <v>50.02</v>
       </c>
       <c r="E21">
-        <v>15.87</v>
+        <v>19.51</v>
       </c>
       <c r="F21">
-        <v>3235.89</v>
+        <v>299.89</v>
       </c>
       <c r="G21">
-        <v>1155</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>416262</v>
+        <v>146195.6</v>
       </c>
       <c r="C22">
-        <v>91.31999999999999</v>
+        <v>70.87</v>
       </c>
       <c r="D22">
-        <v>165.5</v>
+        <v>141.5</v>
       </c>
       <c r="E22">
-        <v>21.01</v>
+        <v>15.87</v>
       </c>
       <c r="F22">
-        <v>2629.8</v>
+        <v>2443.86</v>
       </c>
       <c r="G22">
-        <v>2591</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B23">
-        <v>308</v>
+        <v>416262</v>
       </c>
       <c r="C23">
-        <v>155.17</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="D23">
-        <v>84.36</v>
+        <v>165.5</v>
       </c>
       <c r="E23">
-        <v>72.39</v>
+        <v>21.01</v>
       </c>
       <c r="F23">
-        <v>191.7</v>
+        <v>2629.8</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>308</v>
+      </c>
+      <c r="C24">
+        <v>155.17</v>
+      </c>
+      <c r="D24">
+        <v>84.36</v>
+      </c>
+      <c r="E24">
+        <v>72.39</v>
+      </c>
+      <c r="F24">
+        <v>191.7</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B24">
-        <v>18864.37</v>
-      </c>
-      <c r="C24">
-        <v>53.82</v>
-      </c>
-      <c r="D24">
-        <v>93.31</v>
-      </c>
-      <c r="E24">
+      <c r="B25">
+        <v>19142.95</v>
+      </c>
+      <c r="C25">
+        <v>54.61</v>
+      </c>
+      <c r="D25">
+        <v>102.27</v>
+      </c>
+      <c r="E25">
         <v>13.38</v>
       </c>
-      <c r="F24">
-        <v>925.46</v>
-      </c>
-      <c r="G24">
+      <c r="F25">
+        <v>1097.6</v>
+      </c>
+      <c r="G25">
         <v>198</v>
       </c>
     </row>
@@ -1715,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1787,19 +1837,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>1246248.44</v>
+        <v>1246238.16</v>
       </c>
       <c r="C3">
         <v>73.5</v>
       </c>
       <c r="D3">
-        <v>149.28</v>
+        <v>147.17</v>
       </c>
       <c r="E3">
         <v>9.6</v>
       </c>
       <c r="F3">
-        <v>3235.89</v>
+        <v>3110.69</v>
       </c>
       <c r="G3">
         <v>9799</v>
@@ -1812,13 +1862,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1612487.23</v>
+        <v>1612492.43</v>
       </c>
       <c r="C4">
         <v>109.26</v>
       </c>
       <c r="D4">
-        <v>223.38</v>
+        <v>223.51</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1828,6 +1878,31 @@
       </c>
       <c r="G4">
         <v>8906</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>1616796.5</v>
+      </c>
+      <c r="C5">
+        <v>114.07</v>
+      </c>
+      <c r="D5">
+        <v>236.17</v>
+      </c>
+      <c r="E5">
+        <v>21.01</v>
+      </c>
+      <c r="F5">
+        <v>3443.79</v>
+      </c>
+      <c r="G5">
+        <v>8334</v>
       </c>
     </row>
   </sheetData>
@@ -1837,7 +1912,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1924,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>723</v>
+        <v>631</v>
       </c>
     </row>
     <row r="4">
@@ -1934,19 +2009,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>1246248.44</v>
+        <v>1246238.16</v>
       </c>
       <c r="C4">
         <v>73.5</v>
       </c>
       <c r="D4">
-        <v>149.28</v>
+        <v>147.17</v>
       </c>
       <c r="E4">
         <v>9.6</v>
       </c>
       <c r="F4">
-        <v>3235.89</v>
+        <v>3110.69</v>
       </c>
       <c r="G4">
         <v>9799</v>
@@ -1959,13 +2034,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>1612487.23</v>
+        <v>1612492.43</v>
       </c>
       <c r="C5">
         <v>109.26</v>
       </c>
       <c r="D5">
-        <v>223.38</v>
+        <v>223.51</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1975,6 +2050,31 @@
       </c>
       <c r="G5">
         <v>8906</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Uncategorised</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>1616796.5</v>
+      </c>
+      <c r="C6">
+        <v>114.07</v>
+      </c>
+      <c r="D6">
+        <v>236.17</v>
+      </c>
+      <c r="E6">
+        <v>21.01</v>
+      </c>
+      <c r="F6">
+        <v>3443.79</v>
+      </c>
+      <c r="G6">
+        <v>8334</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP.xlsx
@@ -398,7 +398,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>591.46</v>
+        <v>591.36</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -407,16 +407,16 @@
         <v>9915.709999999999</v>
       </c>
       <c r="D2">
-        <v>711.65</v>
+        <v>712.0599999999999</v>
       </c>
       <c r="E2">
-        <v>498.07</v>
+        <v>498.27</v>
       </c>
       <c r="F2">
-        <v>249.06</v>
+        <v>249.12</v>
       </c>
       <c r="G2">
-        <v>923.27</v>
+        <v>923.35</v>
       </c>
     </row>
   </sheetData>
@@ -468,25 +468,25 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>516.08</v>
+        <v>575.8099999999999</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>9859.190000000001</v>
+        <v>9915.709999999999</v>
       </c>
       <c r="D2">
-        <v>646.03</v>
+        <v>711.47</v>
       </c>
       <c r="E2">
-        <v>432.95</v>
+        <v>480.93</v>
       </c>
       <c r="F2">
-        <v>205.41</v>
+        <v>226.92</v>
       </c>
       <c r="G2">
-        <v>810.6900000000001</v>
+        <v>902.38</v>
       </c>
     </row>
   </sheetData>
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1894830</v>
+        <v>1894788</v>
       </c>
       <c r="C4">
-        <v>110.57</v>
+        <v>110.58</v>
       </c>
       <c r="D4">
-        <v>213.69</v>
+        <v>213.7</v>
       </c>
       <c r="E4">
         <v>21.01</v>
@@ -608,7 +608,7 @@
         <v>7830.88</v>
       </c>
       <c r="G4">
-        <v>9887</v>
+        <v>9886</v>
       </c>
     </row>
     <row r="5">
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>14423094</v>
+        <v>14422464</v>
       </c>
       <c r="C7">
         <v>396.46</v>
       </c>
       <c r="D7">
-        <v>504.87</v>
+        <v>504.88</v>
       </c>
       <c r="E7">
         <v>21.01</v>
@@ -683,7 +683,7 @@
         <v>6976.78</v>
       </c>
       <c r="G7">
-        <v>22581</v>
+        <v>22580</v>
       </c>
     </row>
     <row r="8">
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1616796.5</v>
+        <v>1614525</v>
       </c>
       <c r="C11">
-        <v>114.07</v>
+        <v>113.91</v>
       </c>
       <c r="D11">
-        <v>236.17</v>
+        <v>235.02</v>
       </c>
       <c r="E11">
         <v>21.01</v>
       </c>
       <c r="F11">
-        <v>3443.79</v>
+        <v>5095.68</v>
       </c>
       <c r="G11">
         <v>8334</v>
@@ -818,13 +818,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>11231.5</v>
+        <v>11571.5</v>
       </c>
       <c r="C13">
-        <v>28.45</v>
+        <v>29.31</v>
       </c>
       <c r="D13">
-        <v>62.84</v>
+        <v>63.08</v>
       </c>
       <c r="E13">
         <v>11.76</v>
@@ -1018,19 +1018,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>146195.6</v>
+        <v>143892.88</v>
       </c>
       <c r="C21">
-        <v>70.87</v>
+        <v>69.75</v>
       </c>
       <c r="D21">
-        <v>141.5</v>
+        <v>152.87</v>
       </c>
       <c r="E21">
         <v>15.87</v>
       </c>
       <c r="F21">
-        <v>2443.86</v>
+        <v>3235.89</v>
       </c>
       <c r="G21">
         <v>1155</v>
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="B24">
-        <v>19142.95</v>
+        <v>19426.5</v>
       </c>
       <c r="C24">
-        <v>54.61</v>
+        <v>55.42</v>
       </c>
       <c r="D24">
-        <v>102.27</v>
+        <v>104.9</v>
       </c>
       <c r="E24">
         <v>13.38</v>
@@ -1215,13 +1215,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1894830</v>
+        <v>1894788</v>
       </c>
       <c r="C4">
-        <v>110.57</v>
+        <v>110.58</v>
       </c>
       <c r="D4">
-        <v>213.69</v>
+        <v>213.7</v>
       </c>
       <c r="E4">
         <v>21.01</v>
@@ -1230,7 +1230,7 @@
         <v>7830.88</v>
       </c>
       <c r="G4">
-        <v>9887</v>
+        <v>9886</v>
       </c>
     </row>
     <row r="5">
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>14423094</v>
+        <v>14422464</v>
       </c>
       <c r="C7">
         <v>396.46</v>
       </c>
       <c r="D7">
-        <v>504.87</v>
+        <v>504.88</v>
       </c>
       <c r="E7">
         <v>21.01</v>
@@ -1305,7 +1305,7 @@
         <v>6976.78</v>
       </c>
       <c r="G7">
-        <v>22581</v>
+        <v>22580</v>
       </c>
     </row>
     <row r="8">
@@ -1390,19 +1390,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1616796.5</v>
+        <v>1614525</v>
       </c>
       <c r="C11">
-        <v>114.07</v>
+        <v>113.91</v>
       </c>
       <c r="D11">
-        <v>236.17</v>
+        <v>235.02</v>
       </c>
       <c r="E11">
         <v>21.01</v>
       </c>
       <c r="F11">
-        <v>3443.79</v>
+        <v>5095.68</v>
       </c>
       <c r="G11">
         <v>8334</v>
@@ -1430,7 +1430,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>631</v>
+        <v>732</v>
       </c>
     </row>
     <row r="13">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>11231.5</v>
+        <v>11571.5</v>
       </c>
       <c r="C14">
-        <v>28.45</v>
+        <v>29.31</v>
       </c>
       <c r="D14">
-        <v>62.84</v>
+        <v>63.08</v>
       </c>
       <c r="E14">
         <v>11.76</v>
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>146195.6</v>
+        <v>143892.88</v>
       </c>
       <c r="C22">
-        <v>70.87</v>
+        <v>69.75</v>
       </c>
       <c r="D22">
-        <v>141.5</v>
+        <v>152.87</v>
       </c>
       <c r="E22">
         <v>15.87</v>
       </c>
       <c r="F22">
-        <v>2443.86</v>
+        <v>3235.89</v>
       </c>
       <c r="G22">
         <v>1155</v>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="B25">
-        <v>19142.95</v>
+        <v>19426.5</v>
       </c>
       <c r="C25">
-        <v>54.61</v>
+        <v>55.42</v>
       </c>
       <c r="D25">
-        <v>102.27</v>
+        <v>104.9</v>
       </c>
       <c r="E25">
         <v>13.38</v>
@@ -1812,13 +1812,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>17580276</v>
+        <v>17579604</v>
       </c>
       <c r="C2">
-        <v>478.48</v>
+        <v>478.49</v>
       </c>
       <c r="D2">
-        <v>585.66</v>
+        <v>585.67</v>
       </c>
       <c r="E2">
         <v>21.01</v>
@@ -1827,7 +1827,7 @@
         <v>9557.690000000001</v>
       </c>
       <c r="G2">
-        <v>22825</v>
+        <v>22824</v>
       </c>
     </row>
     <row r="3">
@@ -1837,19 +1837,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>1246238.16</v>
+        <v>1244161.6</v>
       </c>
       <c r="C3">
-        <v>73.5</v>
+        <v>73.38</v>
       </c>
       <c r="D3">
-        <v>147.17</v>
+        <v>148.65</v>
       </c>
       <c r="E3">
         <v>9.6</v>
       </c>
       <c r="F3">
-        <v>3110.69</v>
+        <v>3235.89</v>
       </c>
       <c r="G3">
         <v>9799</v>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1612492.43</v>
+        <v>1612981.39</v>
       </c>
       <c r="C4">
-        <v>109.26</v>
+        <v>109.29</v>
       </c>
       <c r="D4">
-        <v>223.51</v>
+        <v>223.49</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1887,19 +1887,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>1616796.5</v>
+        <v>1614525</v>
       </c>
       <c r="C5">
-        <v>114.07</v>
+        <v>113.91</v>
       </c>
       <c r="D5">
-        <v>236.17</v>
+        <v>235.02</v>
       </c>
       <c r="E5">
         <v>21.01</v>
       </c>
       <c r="F5">
-        <v>3443.79</v>
+        <v>5095.68</v>
       </c>
       <c r="G5">
         <v>8334</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>17580276</v>
+        <v>17579604</v>
       </c>
       <c r="C2">
-        <v>478.48</v>
+        <v>478.49</v>
       </c>
       <c r="D2">
-        <v>585.66</v>
+        <v>585.67</v>
       </c>
       <c r="E2">
         <v>21.01</v>
@@ -1974,7 +1974,7 @@
         <v>9557.690000000001</v>
       </c>
       <c r="G2">
-        <v>22825</v>
+        <v>22824</v>
       </c>
     </row>
     <row r="3">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>631</v>
+        <v>732</v>
       </c>
     </row>
     <row r="4">
@@ -2009,19 +2009,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>1246238.16</v>
+        <v>1244161.6</v>
       </c>
       <c r="C4">
-        <v>73.5</v>
+        <v>73.38</v>
       </c>
       <c r="D4">
-        <v>147.17</v>
+        <v>148.65</v>
       </c>
       <c r="E4">
         <v>9.6</v>
       </c>
       <c r="F4">
-        <v>3110.69</v>
+        <v>3235.89</v>
       </c>
       <c r="G4">
         <v>9799</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>1612492.43</v>
+        <v>1612981.39</v>
       </c>
       <c r="C5">
-        <v>109.26</v>
+        <v>109.29</v>
       </c>
       <c r="D5">
-        <v>223.51</v>
+        <v>223.49</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -2059,19 +2059,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>1616796.5</v>
+        <v>1614525</v>
       </c>
       <c r="C6">
-        <v>114.07</v>
+        <v>113.91</v>
       </c>
       <c r="D6">
-        <v>236.17</v>
+        <v>235.02</v>
       </c>
       <c r="E6">
         <v>21.01</v>
       </c>
       <c r="F6">
-        <v>3443.79</v>
+        <v>5095.68</v>
       </c>
       <c r="G6">
         <v>8334</v>

--- a/OMOP Analysis/Results/Output_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP.xlsx
@@ -398,7 +398,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>591.36</v>
+        <v>591.61</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -407,16 +407,16 @@
         <v>9915.709999999999</v>
       </c>
       <c r="D2">
-        <v>712.0599999999999</v>
+        <v>711.01</v>
       </c>
       <c r="E2">
-        <v>498.27</v>
+        <v>498.57</v>
       </c>
       <c r="F2">
-        <v>249.12</v>
+        <v>248.65</v>
       </c>
       <c r="G2">
-        <v>923.35</v>
+        <v>922.16</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +468,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>575.8099999999999</v>
+        <v>576.0599999999999</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -477,16 +477,16 @@
         <v>9915.709999999999</v>
       </c>
       <c r="D2">
-        <v>711.47</v>
+        <v>710.46</v>
       </c>
       <c r="E2">
-        <v>480.93</v>
+        <v>480.76</v>
       </c>
       <c r="F2">
-        <v>226.92</v>
+        <v>226.48</v>
       </c>
       <c r="G2">
-        <v>902.38</v>
+        <v>901.78</v>
       </c>
     </row>
   </sheetData>
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1614525</v>
+        <v>1623318.12</v>
       </c>
       <c r="C11">
-        <v>113.91</v>
+        <v>114.53</v>
       </c>
       <c r="D11">
-        <v>235.02</v>
+        <v>229.36</v>
       </c>
       <c r="E11">
-        <v>21.01</v>
+        <v>24.71</v>
       </c>
       <c r="F11">
-        <v>5095.68</v>
+        <v>3519.23</v>
       </c>
       <c r="G11">
         <v>8334</v>
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>11571.5</v>
+        <v>11414</v>
       </c>
       <c r="C13">
-        <v>29.31</v>
+        <v>28.91</v>
       </c>
       <c r="D13">
-        <v>63.08</v>
+        <v>61.35</v>
       </c>
       <c r="E13">
-        <v>11.76</v>
+        <v>13.01</v>
       </c>
       <c r="F13">
-        <v>533.83</v>
+        <v>487</v>
       </c>
       <c r="G13">
         <v>231</v>
@@ -1018,19 +1018,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>143892.88</v>
+        <v>145265.26</v>
       </c>
       <c r="C21">
-        <v>69.75</v>
+        <v>70.42</v>
       </c>
       <c r="D21">
-        <v>152.87</v>
+        <v>145.74</v>
       </c>
       <c r="E21">
-        <v>15.87</v>
+        <v>18.44</v>
       </c>
       <c r="F21">
-        <v>3235.89</v>
+        <v>2839.88</v>
       </c>
       <c r="G21">
         <v>1155</v>
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>19426.5</v>
+        <v>18648.74</v>
       </c>
       <c r="C24">
-        <v>55.42</v>
+        <v>53.2</v>
       </c>
       <c r="D24">
-        <v>104.9</v>
+        <v>97.72</v>
       </c>
       <c r="E24">
-        <v>13.38</v>
+        <v>14.63</v>
       </c>
       <c r="F24">
-        <v>1097.6</v>
+        <v>1011.43</v>
       </c>
       <c r="G24">
         <v>198</v>
@@ -1390,19 +1390,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>1614525</v>
+        <v>1623318.12</v>
       </c>
       <c r="C11">
-        <v>113.91</v>
+        <v>114.53</v>
       </c>
       <c r="D11">
-        <v>235.02</v>
+        <v>229.36</v>
       </c>
       <c r="E11">
-        <v>21.01</v>
+        <v>24.71</v>
       </c>
       <c r="F11">
-        <v>5095.68</v>
+        <v>3519.23</v>
       </c>
       <c r="G11">
         <v>8334</v>
@@ -1465,19 +1465,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>11571.5</v>
+        <v>11414</v>
       </c>
       <c r="C14">
-        <v>29.31</v>
+        <v>28.91</v>
       </c>
       <c r="D14">
-        <v>63.08</v>
+        <v>61.35</v>
       </c>
       <c r="E14">
-        <v>11.76</v>
+        <v>13.01</v>
       </c>
       <c r="F14">
-        <v>533.83</v>
+        <v>487</v>
       </c>
       <c r="G14">
         <v>231</v>
@@ -1665,19 +1665,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>143892.88</v>
+        <v>145265.26</v>
       </c>
       <c r="C22">
-        <v>69.75</v>
+        <v>70.42</v>
       </c>
       <c r="D22">
-        <v>152.87</v>
+        <v>145.74</v>
       </c>
       <c r="E22">
-        <v>15.87</v>
+        <v>18.44</v>
       </c>
       <c r="F22">
-        <v>3235.89</v>
+        <v>2839.88</v>
       </c>
       <c r="G22">
         <v>1155</v>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>19426.5</v>
+        <v>18648.74</v>
       </c>
       <c r="C25">
-        <v>55.42</v>
+        <v>53.2</v>
       </c>
       <c r="D25">
-        <v>104.9</v>
+        <v>97.72</v>
       </c>
       <c r="E25">
-        <v>13.38</v>
+        <v>14.63</v>
       </c>
       <c r="F25">
-        <v>1097.6</v>
+        <v>1011.43</v>
       </c>
       <c r="G25">
         <v>198</v>
@@ -1837,19 +1837,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>1244161.6</v>
+        <v>1246032.56</v>
       </c>
       <c r="C3">
-        <v>73.38</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D3">
-        <v>148.65</v>
+        <v>147.9</v>
       </c>
       <c r="E3">
         <v>9.6</v>
       </c>
       <c r="F3">
-        <v>3235.89</v>
+        <v>3110.69</v>
       </c>
       <c r="G3">
         <v>9799</v>
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1612981.39</v>
+        <v>1612182.98</v>
       </c>
       <c r="C4">
-        <v>109.29</v>
+        <v>109.24</v>
       </c>
       <c r="D4">
-        <v>223.49</v>
+        <v>223.4</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1887,19 +1887,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>1614525</v>
+        <v>1623318.12</v>
       </c>
       <c r="C5">
-        <v>113.91</v>
+        <v>114.53</v>
       </c>
       <c r="D5">
-        <v>235.02</v>
+        <v>229.36</v>
       </c>
       <c r="E5">
-        <v>21.01</v>
+        <v>24.71</v>
       </c>
       <c r="F5">
-        <v>5095.68</v>
+        <v>3519.23</v>
       </c>
       <c r="G5">
         <v>8334</v>
@@ -2009,19 +2009,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>1244161.6</v>
+        <v>1246032.56</v>
       </c>
       <c r="C4">
-        <v>73.38</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="D4">
-        <v>148.65</v>
+        <v>147.9</v>
       </c>
       <c r="E4">
         <v>9.6</v>
       </c>
       <c r="F4">
-        <v>3235.89</v>
+        <v>3110.69</v>
       </c>
       <c r="G4">
         <v>9799</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>1612981.39</v>
+        <v>1612182.98</v>
       </c>
       <c r="C5">
-        <v>109.29</v>
+        <v>109.24</v>
       </c>
       <c r="D5">
-        <v>223.49</v>
+        <v>223.4</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -2059,19 +2059,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>1614525</v>
+        <v>1623318.12</v>
       </c>
       <c r="C6">
-        <v>113.91</v>
+        <v>114.53</v>
       </c>
       <c r="D6">
-        <v>235.02</v>
+        <v>229.36</v>
       </c>
       <c r="E6">
-        <v>21.01</v>
+        <v>24.71</v>
       </c>
       <c r="F6">
-        <v>5095.68</v>
+        <v>3519.23</v>
       </c>
       <c r="G6">
         <v>8334</v>

--- a/OMOP Analysis/Results/Output_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP.xlsx
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>429</v>
+        <v>572</v>
       </c>
       <c r="C2">
         <v>71.55</v>
       </c>
       <c r="D2">
-        <v>61.96</v>
+        <v>50.59</v>
       </c>
       <c r="E2">
         <v>35.77</v>
@@ -416,7 +416,7 @@
         <v>143.1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -426,22 +426,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>211422.45</v>
+        <v>317254.03</v>
       </c>
       <c r="C3">
-        <v>52.68</v>
+        <v>61.09</v>
       </c>
       <c r="D3">
-        <v>114.07</v>
+        <v>114.75</v>
       </c>
       <c r="E3">
         <v>13.38</v>
       </c>
       <c r="F3">
-        <v>1575.61</v>
+        <v>1594.9</v>
       </c>
       <c r="G3">
-        <v>2343</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
@@ -451,22 +451,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>1286082</v>
+        <v>1801842</v>
       </c>
       <c r="C4">
-        <v>111</v>
+        <v>123.6</v>
       </c>
       <c r="D4">
-        <v>222.85</v>
+        <v>230.89</v>
       </c>
       <c r="E4">
         <v>21.01</v>
       </c>
       <c r="F4">
-        <v>5037.18</v>
+        <v>7830.88</v>
       </c>
       <c r="G4">
-        <v>6790</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>556178.48</v>
+        <v>708846.84</v>
       </c>
       <c r="C5">
-        <v>151</v>
+        <v>167.29</v>
       </c>
       <c r="D5">
-        <v>303.68</v>
+        <v>305.44</v>
       </c>
       <c r="E5">
         <v>15.87</v>
@@ -491,7 +491,7 @@
         <v>2457.58</v>
       </c>
       <c r="G5">
-        <v>2269</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
@@ -501,22 +501,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>1310.53</v>
+        <v>2407.09</v>
       </c>
       <c r="C6">
-        <v>36.55</v>
+        <v>59.3</v>
       </c>
       <c r="D6">
-        <v>27.36</v>
+        <v>104.19</v>
       </c>
       <c r="E6">
         <v>13.38</v>
       </c>
       <c r="F6">
-        <v>103.65</v>
+        <v>375.72</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>9553950</v>
+        <v>13688724</v>
       </c>
       <c r="C7">
-        <v>391.64</v>
+        <v>471.45</v>
       </c>
       <c r="D7">
-        <v>533.6900000000001</v>
+        <v>531.6</v>
       </c>
       <c r="E7">
         <v>21.01</v>
@@ -541,7 +541,7 @@
         <v>6976.78</v>
       </c>
       <c r="G7">
-        <v>16314</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>2014</v>
+        <v>2703</v>
       </c>
       <c r="C8">
-        <v>242.54</v>
+        <v>178.95</v>
       </c>
       <c r="D8">
-        <v>416.14</v>
+        <v>270.76</v>
       </c>
       <c r="E8">
-        <v>79.55</v>
+        <v>26.52</v>
       </c>
       <c r="F8">
-        <v>1209.89</v>
+        <v>1032.44</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>512210.97</v>
+        <v>704057.33</v>
       </c>
       <c r="C9">
-        <v>89.11</v>
+        <v>96.95</v>
       </c>
       <c r="D9">
-        <v>213.33</v>
+        <v>186.79</v>
       </c>
       <c r="E9">
         <v>9.6</v>
       </c>
       <c r="F9">
-        <v>2139.07</v>
+        <v>2164.59</v>
       </c>
       <c r="G9">
-        <v>3723</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>63.44</v>
+        <v>95.16</v>
       </c>
       <c r="C10">
         <v>15.87</v>
@@ -616,7 +616,7 @@
         <v>15.87</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -626,22 +626,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>1065077.22</v>
+        <v>1531076.28</v>
       </c>
       <c r="C11">
-        <v>115.36</v>
+        <v>129.54</v>
       </c>
       <c r="D11">
-        <v>268.99</v>
+        <v>250.23</v>
       </c>
       <c r="E11">
         <v>24.71</v>
       </c>
       <c r="F11">
-        <v>3435.44</v>
+        <v>3519.23</v>
       </c>
       <c r="G11">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="B12">
-        <v>26279.53</v>
+        <v>36779.83</v>
       </c>
       <c r="C12">
-        <v>35.96</v>
+        <v>38.6</v>
       </c>
       <c r="D12">
-        <v>87.23999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="E12">
         <v>9.6</v>
@@ -666,7 +666,7 @@
         <v>855.05</v>
       </c>
       <c r="G12">
-        <v>421</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13">
@@ -676,22 +676,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>8294</v>
+        <v>11076</v>
       </c>
       <c r="C13">
-        <v>29.33</v>
+        <v>38.66</v>
       </c>
       <c r="D13">
-        <v>67.58</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="E13">
         <v>13.01</v>
       </c>
       <c r="F13">
-        <v>487</v>
+        <v>575.55</v>
       </c>
       <c r="G13">
-        <v>169</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>30294</v>
+        <v>36564</v>
       </c>
       <c r="C14">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D14">
-        <v>45.76</v>
+        <v>41.68</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -716,7 +716,7 @@
         <v>483.93</v>
       </c>
       <c r="G14">
-        <v>841</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="15">
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B15">
-        <v>12546</v>
+        <v>19188</v>
       </c>
       <c r="C15">
-        <v>58.18</v>
+        <v>70.73</v>
       </c>
       <c r="D15">
-        <v>97.95999999999999</v>
+        <v>114.89</v>
       </c>
       <c r="E15">
         <v>20.51</v>
       </c>
       <c r="F15">
-        <v>902.12</v>
+        <v>981.98</v>
       </c>
       <c r="G15">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="B16">
-        <v>824964</v>
+        <v>1191456</v>
       </c>
       <c r="C16">
-        <v>90.09999999999999</v>
+        <v>101.96</v>
       </c>
       <c r="D16">
-        <v>175.83</v>
+        <v>170.23</v>
       </c>
       <c r="E16">
         <v>21.01</v>
@@ -766,7 +766,7 @@
         <v>3334.89</v>
       </c>
       <c r="G16">
-        <v>5299</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="17">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>3690</v>
+        <v>4592</v>
       </c>
       <c r="C17">
-        <v>43.57</v>
+        <v>44.43</v>
       </c>
       <c r="D17">
-        <v>43.06</v>
+        <v>47.7</v>
       </c>
       <c r="E17">
         <v>20.51</v>
@@ -791,7 +791,7 @@
         <v>225.65</v>
       </c>
       <c r="G17">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>3157</v>
+        <v>5781</v>
       </c>
       <c r="C18">
-        <v>94.75</v>
+        <v>118.76</v>
       </c>
       <c r="D18">
-        <v>96.13</v>
+        <v>130.9</v>
       </c>
       <c r="E18">
         <v>20.51</v>
       </c>
       <c r="F18">
-        <v>389.77</v>
+        <v>615.42</v>
       </c>
       <c r="G18">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
@@ -826,22 +826,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>194975.33</v>
+        <v>291723.95</v>
       </c>
       <c r="C19">
-        <v>43.98</v>
+        <v>51.31</v>
       </c>
       <c r="D19">
-        <v>110.02</v>
+        <v>114.35</v>
       </c>
       <c r="E19">
         <v>9.6</v>
       </c>
       <c r="F19">
-        <v>1882.51</v>
+        <v>3110.69</v>
       </c>
       <c r="G19">
-        <v>2605</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="20">
@@ -851,22 +851,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>1950</v>
+        <v>2925</v>
       </c>
       <c r="C20">
-        <v>31.44</v>
+        <v>35.23</v>
       </c>
       <c r="D20">
-        <v>55.18</v>
+        <v>58.73</v>
       </c>
       <c r="E20">
         <v>19.51</v>
       </c>
       <c r="F20">
-        <v>299.89</v>
+        <v>344.08</v>
       </c>
       <c r="G20">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>99816.88</v>
+        <v>141837.28</v>
       </c>
       <c r="C21">
-        <v>72.40000000000001</v>
+        <v>81.11</v>
       </c>
       <c r="D21">
-        <v>154.55</v>
+        <v>184.62</v>
       </c>
       <c r="E21">
         <v>18.44</v>
       </c>
       <c r="F21">
-        <v>1835.88</v>
+        <v>2839.88</v>
       </c>
       <c r="G21">
-        <v>781</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="22">
@@ -901,22 +901,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>281568</v>
+        <v>405048</v>
       </c>
       <c r="C22">
-        <v>91.3</v>
+        <v>104.1</v>
       </c>
       <c r="D22">
-        <v>184.22</v>
+        <v>245.03</v>
       </c>
       <c r="E22">
         <v>21.01</v>
       </c>
       <c r="F22">
-        <v>1956.7</v>
+        <v>6136.2</v>
       </c>
       <c r="G22">
-        <v>1765</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="23">
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>14264.24</v>
+        <v>17333.39</v>
       </c>
       <c r="C24">
-        <v>56.55</v>
+        <v>63.14</v>
       </c>
       <c r="D24">
-        <v>118.14</v>
+        <v>119.82</v>
       </c>
       <c r="E24">
         <v>14.63</v>
       </c>
       <c r="F24">
-        <v>928.37</v>
+        <v>1011.43</v>
       </c>
       <c r="G24">
-        <v>144</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1023,13 +1023,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>429</v>
+        <v>572</v>
       </c>
       <c r="C2">
         <v>71.55</v>
       </c>
       <c r="D2">
-        <v>61.96</v>
+        <v>50.59</v>
       </c>
       <c r="E2">
         <v>35.77</v>
@@ -1038,7 +1038,7 @@
         <v>143.1</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>211422.45</v>
+        <v>317254.03</v>
       </c>
       <c r="C3">
-        <v>52.68</v>
+        <v>61.09</v>
       </c>
       <c r="D3">
-        <v>114.07</v>
+        <v>114.75</v>
       </c>
       <c r="E3">
         <v>13.38</v>
       </c>
       <c r="F3">
-        <v>1575.61</v>
+        <v>1594.9</v>
       </c>
       <c r="G3">
-        <v>2343</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>1286082</v>
+        <v>1801842</v>
       </c>
       <c r="C4">
-        <v>111</v>
+        <v>123.6</v>
       </c>
       <c r="D4">
-        <v>222.85</v>
+        <v>230.89</v>
       </c>
       <c r="E4">
         <v>21.01</v>
       </c>
       <c r="F4">
-        <v>5037.18</v>
+        <v>7830.88</v>
       </c>
       <c r="G4">
-        <v>6790</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>556178.48</v>
+        <v>708846.84</v>
       </c>
       <c r="C5">
-        <v>151</v>
+        <v>167.29</v>
       </c>
       <c r="D5">
-        <v>303.68</v>
+        <v>305.44</v>
       </c>
       <c r="E5">
         <v>15.87</v>
@@ -1113,7 +1113,7 @@
         <v>2457.58</v>
       </c>
       <c r="G5">
-        <v>2269</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>1310.53</v>
+        <v>2407.09</v>
       </c>
       <c r="C6">
-        <v>36.55</v>
+        <v>59.3</v>
       </c>
       <c r="D6">
-        <v>27.36</v>
+        <v>104.19</v>
       </c>
       <c r="E6">
         <v>13.38</v>
       </c>
       <c r="F6">
-        <v>103.65</v>
+        <v>375.72</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>9553950</v>
+        <v>13688724</v>
       </c>
       <c r="C7">
-        <v>391.64</v>
+        <v>471.45</v>
       </c>
       <c r="D7">
-        <v>533.6900000000001</v>
+        <v>531.6</v>
       </c>
       <c r="E7">
         <v>21.01</v>
@@ -1163,7 +1163,7 @@
         <v>6976.78</v>
       </c>
       <c r="G7">
-        <v>16314</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>2014</v>
+        <v>2703</v>
       </c>
       <c r="C8">
-        <v>242.54</v>
+        <v>178.95</v>
       </c>
       <c r="D8">
-        <v>416.14</v>
+        <v>270.76</v>
       </c>
       <c r="E8">
-        <v>79.55</v>
+        <v>26.52</v>
       </c>
       <c r="F8">
-        <v>1209.89</v>
+        <v>1032.44</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>512210.97</v>
+        <v>704057.33</v>
       </c>
       <c r="C9">
-        <v>89.11</v>
+        <v>96.95</v>
       </c>
       <c r="D9">
-        <v>213.33</v>
+        <v>186.79</v>
       </c>
       <c r="E9">
         <v>9.6</v>
       </c>
       <c r="F9">
-        <v>2139.07</v>
+        <v>2164.59</v>
       </c>
       <c r="G9">
-        <v>3723</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>63.44</v>
+        <v>95.16</v>
       </c>
       <c r="C10">
         <v>15.87</v>
@@ -1238,7 +1238,7 @@
         <v>15.87</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>1065077.22</v>
+        <v>1531076.28</v>
       </c>
       <c r="C11">
-        <v>115.36</v>
+        <v>129.54</v>
       </c>
       <c r="D11">
-        <v>268.99</v>
+        <v>250.23</v>
       </c>
       <c r="E11">
         <v>24.71</v>
       </c>
       <c r="F11">
-        <v>3435.44</v>
+        <v>3519.23</v>
       </c>
       <c r="G11">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>727</v>
+        <v>621</v>
       </c>
     </row>
     <row r="13">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>26279.53</v>
+        <v>36779.83</v>
       </c>
       <c r="C13">
-        <v>35.96</v>
+        <v>38.6</v>
       </c>
       <c r="D13">
-        <v>87.23999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="E13">
         <v>9.6</v>
@@ -1313,7 +1313,7 @@
         <v>855.05</v>
       </c>
       <c r="G13">
-        <v>421</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>8294</v>
+        <v>11076</v>
       </c>
       <c r="C14">
-        <v>29.33</v>
+        <v>38.66</v>
       </c>
       <c r="D14">
-        <v>67.58</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="E14">
         <v>13.01</v>
       </c>
       <c r="F14">
-        <v>487</v>
+        <v>575.55</v>
       </c>
       <c r="G14">
-        <v>169</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
@@ -1348,13 +1348,13 @@
         </is>
       </c>
       <c r="B15">
-        <v>30294</v>
+        <v>36564</v>
       </c>
       <c r="C15">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D15">
-        <v>45.76</v>
+        <v>41.68</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1363,7 +1363,7 @@
         <v>483.93</v>
       </c>
       <c r="G15">
-        <v>841</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="16">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>12546</v>
+        <v>19188</v>
       </c>
       <c r="C16">
-        <v>58.18</v>
+        <v>70.73</v>
       </c>
       <c r="D16">
-        <v>97.95999999999999</v>
+        <v>114.89</v>
       </c>
       <c r="E16">
         <v>20.51</v>
       </c>
       <c r="F16">
-        <v>902.12</v>
+        <v>981.98</v>
       </c>
       <c r="G16">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>824964</v>
+        <v>1191456</v>
       </c>
       <c r="C17">
-        <v>90.09999999999999</v>
+        <v>101.96</v>
       </c>
       <c r="D17">
-        <v>175.83</v>
+        <v>170.23</v>
       </c>
       <c r="E17">
         <v>21.01</v>
@@ -1413,7 +1413,7 @@
         <v>3334.89</v>
       </c>
       <c r="G17">
-        <v>5299</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="18">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>3690</v>
+        <v>4592</v>
       </c>
       <c r="C18">
-        <v>43.57</v>
+        <v>44.43</v>
       </c>
       <c r="D18">
-        <v>43.06</v>
+        <v>47.7</v>
       </c>
       <c r="E18">
         <v>20.51</v>
@@ -1438,7 +1438,7 @@
         <v>225.65</v>
       </c>
       <c r="G18">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>3157</v>
+        <v>5781</v>
       </c>
       <c r="C19">
-        <v>94.75</v>
+        <v>118.76</v>
       </c>
       <c r="D19">
-        <v>96.13</v>
+        <v>130.9</v>
       </c>
       <c r="E19">
         <v>20.51</v>
       </c>
       <c r="F19">
-        <v>389.77</v>
+        <v>615.42</v>
       </c>
       <c r="G19">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>194975.33</v>
+        <v>291723.95</v>
       </c>
       <c r="C20">
-        <v>43.98</v>
+        <v>51.31</v>
       </c>
       <c r="D20">
-        <v>110.02</v>
+        <v>114.35</v>
       </c>
       <c r="E20">
         <v>9.6</v>
       </c>
       <c r="F20">
-        <v>1882.51</v>
+        <v>3110.69</v>
       </c>
       <c r="G20">
-        <v>2605</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="21">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1950</v>
+        <v>2925</v>
       </c>
       <c r="C21">
-        <v>31.44</v>
+        <v>35.23</v>
       </c>
       <c r="D21">
-        <v>55.18</v>
+        <v>58.73</v>
       </c>
       <c r="E21">
         <v>19.51</v>
       </c>
       <c r="F21">
-        <v>299.89</v>
+        <v>344.08</v>
       </c>
       <c r="G21">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>99816.88</v>
+        <v>141837.28</v>
       </c>
       <c r="C22">
-        <v>72.40000000000001</v>
+        <v>81.11</v>
       </c>
       <c r="D22">
-        <v>154.55</v>
+        <v>184.62</v>
       </c>
       <c r="E22">
         <v>18.44</v>
       </c>
       <c r="F22">
-        <v>1835.88</v>
+        <v>2839.88</v>
       </c>
       <c r="G22">
-        <v>781</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>281568</v>
+        <v>405048</v>
       </c>
       <c r="C23">
-        <v>91.3</v>
+        <v>104.1</v>
       </c>
       <c r="D23">
-        <v>184.22</v>
+        <v>245.03</v>
       </c>
       <c r="E23">
         <v>21.01</v>
       </c>
       <c r="F23">
-        <v>1956.7</v>
+        <v>6136.2</v>
       </c>
       <c r="G23">
-        <v>1765</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="24">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>14264.24</v>
+        <v>17333.39</v>
       </c>
       <c r="C25">
-        <v>56.55</v>
+        <v>63.14</v>
       </c>
       <c r="D25">
-        <v>118.14</v>
+        <v>119.82</v>
       </c>
       <c r="E25">
         <v>14.63</v>
       </c>
       <c r="F25">
-        <v>928.37</v>
+        <v>1011.43</v>
       </c>
       <c r="G25">
-        <v>144</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1670,22 +1670,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>11664996</v>
+        <v>16682022</v>
       </c>
       <c r="C2">
-        <v>472.57</v>
+        <v>570.11</v>
       </c>
       <c r="D2">
-        <v>616.0700000000001</v>
+        <v>615.84</v>
       </c>
       <c r="E2">
         <v>21.01</v>
       </c>
       <c r="F2">
-        <v>8700.58</v>
+        <v>9557.690000000001</v>
       </c>
       <c r="G2">
-        <v>16544</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
@@ -1695,22 +1695,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>817387.16</v>
+        <v>1192853.87</v>
       </c>
       <c r="C3">
-        <v>73.11</v>
+        <v>84.59</v>
       </c>
       <c r="D3">
-        <v>160.23</v>
+        <v>189.85</v>
       </c>
       <c r="E3">
         <v>9.6</v>
       </c>
       <c r="F3">
-        <v>2773.9</v>
+        <v>6136.2</v>
       </c>
       <c r="G3">
-        <v>6564</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="4">
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1156933.62</v>
+        <v>1524367.08</v>
       </c>
       <c r="C4">
-        <v>113.54</v>
+        <v>122.12</v>
       </c>
       <c r="D4">
-        <v>253.69</v>
+        <v>241.63</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1735,7 +1735,7 @@
         <v>2457.58</v>
       </c>
       <c r="G4">
-        <v>6458</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="5">
@@ -1745,22 +1745,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1065077.22</v>
+        <v>1531076.28</v>
       </c>
       <c r="C5">
-        <v>115.36</v>
+        <v>129.54</v>
       </c>
       <c r="D5">
-        <v>268.99</v>
+        <v>250.23</v>
       </c>
       <c r="E5">
         <v>24.71</v>
       </c>
       <c r="F5">
-        <v>3435.44</v>
+        <v>3519.23</v>
       </c>
       <c r="G5">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
   </sheetData>
@@ -1817,22 +1817,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>11664996</v>
+        <v>16682022</v>
       </c>
       <c r="C2">
-        <v>472.57</v>
+        <v>570.11</v>
       </c>
       <c r="D2">
-        <v>616.0700000000001</v>
+        <v>615.84</v>
       </c>
       <c r="E2">
         <v>21.01</v>
       </c>
       <c r="F2">
-        <v>8700.58</v>
+        <v>9557.690000000001</v>
       </c>
       <c r="G2">
-        <v>16544</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>727</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4">
@@ -1867,22 +1867,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>817387.16</v>
+        <v>1192853.87</v>
       </c>
       <c r="C4">
-        <v>73.11</v>
+        <v>84.59</v>
       </c>
       <c r="D4">
-        <v>160.23</v>
+        <v>189.85</v>
       </c>
       <c r="E4">
         <v>9.6</v>
       </c>
       <c r="F4">
-        <v>2773.9</v>
+        <v>6136.2</v>
       </c>
       <c r="G4">
-        <v>6564</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="5">
@@ -1892,13 +1892,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>1156933.62</v>
+        <v>1524367.08</v>
       </c>
       <c r="C5">
-        <v>113.54</v>
+        <v>122.12</v>
       </c>
       <c r="D5">
-        <v>253.69</v>
+        <v>241.63</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -1907,7 +1907,7 @@
         <v>2457.58</v>
       </c>
       <c r="G5">
-        <v>6458</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="6">
@@ -1917,22 +1917,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>1065077.22</v>
+        <v>1531076.28</v>
       </c>
       <c r="C6">
-        <v>115.36</v>
+        <v>129.54</v>
       </c>
       <c r="D6">
-        <v>268.99</v>
+        <v>250.23</v>
       </c>
       <c r="E6">
         <v>24.71</v>
       </c>
       <c r="F6">
-        <v>3435.44</v>
+        <v>3519.23</v>
       </c>
       <c r="G6">
-        <v>5605</v>
+        <v>7891</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,19 +401,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>572</v>
+        <v>786.5</v>
       </c>
       <c r="C2">
-        <v>71.55</v>
+        <v>98.38</v>
       </c>
       <c r="D2">
-        <v>50.59</v>
+        <v>84.53</v>
       </c>
       <c r="E2">
         <v>35.77</v>
       </c>
       <c r="F2">
-        <v>143.1</v>
+        <v>214.65</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -422,551 +422,801 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Case Manager / Care Coordinator</t>
         </is>
       </c>
       <c r="B3">
-        <v>317254.03</v>
+        <v>1273077.56</v>
       </c>
       <c r="C3">
-        <v>61.09</v>
+        <v>79.55</v>
       </c>
       <c r="D3">
-        <v>114.75</v>
+        <v>178.25</v>
       </c>
       <c r="E3">
-        <v>13.38</v>
+        <v>2.63</v>
       </c>
       <c r="F3">
-        <v>1594.9</v>
+        <v>2704.94</v>
       </c>
       <c r="G3">
-        <v>3427</v>
+        <v>11268</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B4">
-        <v>1801842</v>
+        <v>1353799.07</v>
       </c>
       <c r="C4">
-        <v>123.6</v>
+        <v>260.7</v>
       </c>
       <c r="D4">
-        <v>230.89</v>
+        <v>497.99</v>
       </c>
       <c r="E4">
-        <v>21.01</v>
+        <v>13.38</v>
       </c>
       <c r="F4">
-        <v>7830.88</v>
+        <v>6620.15</v>
       </c>
       <c r="G4">
-        <v>9405</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B5">
-        <v>708846.84</v>
+        <v>8912484</v>
       </c>
       <c r="C5">
-        <v>167.29</v>
+        <v>611.37</v>
       </c>
       <c r="D5">
-        <v>305.44</v>
+        <v>1088.62</v>
       </c>
       <c r="E5">
-        <v>15.87</v>
+        <v>21.01</v>
       </c>
       <c r="F5">
-        <v>2457.58</v>
+        <v>23412.33</v>
       </c>
       <c r="G5">
-        <v>2879</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B6">
-        <v>2407.09</v>
+        <v>150858.91</v>
       </c>
       <c r="C6">
-        <v>59.3</v>
+        <v>35.6</v>
       </c>
       <c r="D6">
-        <v>104.19</v>
+        <v>88.27</v>
       </c>
       <c r="E6">
-        <v>13.38</v>
+        <v>1.27</v>
       </c>
       <c r="F6">
-        <v>375.72</v>
+        <v>2407.93</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B7">
-        <v>13688724</v>
+        <v>10243.49</v>
       </c>
       <c r="C7">
-        <v>471.45</v>
+        <v>252.34</v>
       </c>
       <c r="D7">
-        <v>531.6</v>
+        <v>438.39</v>
       </c>
       <c r="E7">
-        <v>21.01</v>
+        <v>13.38</v>
       </c>
       <c r="F7">
-        <v>6976.78</v>
+        <v>2254.33</v>
       </c>
       <c r="G7">
-        <v>21658</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B8">
-        <v>2703</v>
+        <v>38198328</v>
       </c>
       <c r="C8">
-        <v>178.95</v>
+        <v>1315.59</v>
       </c>
       <c r="D8">
-        <v>270.76</v>
+        <v>1692.52</v>
       </c>
       <c r="E8">
-        <v>26.52</v>
+        <v>21.01</v>
       </c>
       <c r="F8">
-        <v>1032.44</v>
+        <v>29573.95</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>Health Information Technician</t>
         </is>
       </c>
       <c r="B9">
-        <v>704057.33</v>
+        <v>94819.45</v>
       </c>
       <c r="C9">
-        <v>96.95</v>
+        <v>28.02</v>
       </c>
       <c r="D9">
-        <v>186.79</v>
+        <v>47.42</v>
       </c>
       <c r="E9">
-        <v>9.6</v>
+        <v>0.64</v>
       </c>
       <c r="F9">
-        <v>2164.59</v>
+        <v>406.76</v>
       </c>
       <c r="G9">
-        <v>4954</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B10">
-        <v>95.16</v>
+        <v>6996</v>
       </c>
       <c r="C10">
-        <v>15.87</v>
+        <v>463.17</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>696.08</v>
       </c>
       <c r="E10">
-        <v>15.87</v>
+        <v>26.52</v>
       </c>
       <c r="F10">
-        <v>15.87</v>
+        <v>2581.1</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B11">
-        <v>1531076.28</v>
+        <v>2318108.34</v>
       </c>
       <c r="C11">
-        <v>129.54</v>
+        <v>319.22</v>
       </c>
       <c r="D11">
-        <v>250.23</v>
+        <v>670.22</v>
       </c>
       <c r="E11">
-        <v>24.71</v>
+        <v>9.6</v>
       </c>
       <c r="F11">
-        <v>3519.23</v>
+        <v>9143.24</v>
       </c>
       <c r="G11">
-        <v>7891</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B12">
-        <v>36779.83</v>
+        <v>126.88</v>
       </c>
       <c r="C12">
-        <v>38.6</v>
+        <v>21.16</v>
       </c>
       <c r="D12">
-        <v>80.91</v>
+        <v>9.16</v>
       </c>
       <c r="E12">
-        <v>9.6</v>
+        <v>15.87</v>
       </c>
       <c r="F12">
-        <v>855.05</v>
+        <v>31.74</v>
       </c>
       <c r="G12">
-        <v>616</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B13">
-        <v>11076</v>
+        <v>4332255.54</v>
       </c>
       <c r="C13">
-        <v>38.66</v>
+        <v>366.54</v>
       </c>
       <c r="D13">
-        <v>76.81999999999999</v>
+        <v>817.64</v>
       </c>
       <c r="E13">
-        <v>13.01</v>
+        <v>24.71</v>
       </c>
       <c r="F13">
-        <v>575.55</v>
+        <v>20722.26</v>
       </c>
       <c r="G13">
-        <v>220</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B14">
-        <v>36564</v>
+        <v>191424.05</v>
       </c>
       <c r="C14">
-        <v>21.5</v>
+        <v>200.92</v>
       </c>
       <c r="D14">
-        <v>41.68</v>
+        <v>387.43</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="F14">
-        <v>483.93</v>
+        <v>3580.29</v>
       </c>
       <c r="G14">
-        <v>1125</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Other Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>19188</v>
+        <v>1053829.64</v>
       </c>
       <c r="C15">
-        <v>70.73</v>
+        <v>54.61</v>
       </c>
       <c r="D15">
-        <v>114.89</v>
+        <v>118.58</v>
       </c>
       <c r="E15">
-        <v>20.51</v>
+        <v>1.91</v>
       </c>
       <c r="F15">
-        <v>981.98</v>
+        <v>3255.32</v>
       </c>
       <c r="G15">
-        <v>175</v>
+        <v>13599</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B16">
-        <v>1191456</v>
+        <v>55900</v>
       </c>
       <c r="C16">
-        <v>101.96</v>
+        <v>195.12</v>
       </c>
       <c r="D16">
-        <v>170.23</v>
+        <v>492.29</v>
       </c>
       <c r="E16">
-        <v>21.01</v>
+        <v>13.01</v>
       </c>
       <c r="F16">
-        <v>3334.89</v>
+        <v>2984.61</v>
       </c>
       <c r="G16">
-        <v>7644</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="B17">
-        <v>4592</v>
+        <v>23296.73</v>
       </c>
       <c r="C17">
-        <v>44.43</v>
+        <v>6.69</v>
       </c>
       <c r="D17">
-        <v>47.7</v>
+        <v>13.79</v>
       </c>
       <c r="E17">
-        <v>20.51</v>
+        <v>0.82</v>
       </c>
       <c r="F17">
-        <v>225.65</v>
+        <v>200.72</v>
       </c>
       <c r="G17">
-        <v>61</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B18">
-        <v>5781</v>
+        <v>116364</v>
       </c>
       <c r="C18">
-        <v>118.76</v>
+        <v>68.42</v>
       </c>
       <c r="D18">
-        <v>130.9</v>
+        <v>141.43</v>
       </c>
       <c r="E18">
-        <v>20.51</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>615.42</v>
+        <v>1603.54</v>
       </c>
       <c r="G18">
-        <v>29</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Phlebotomist</t>
         </is>
       </c>
       <c r="B19">
-        <v>291723.95</v>
+        <v>34036.34</v>
       </c>
       <c r="C19">
-        <v>51.31</v>
+        <v>11.62</v>
       </c>
       <c r="D19">
-        <v>114.35</v>
+        <v>24.28</v>
       </c>
       <c r="E19">
-        <v>9.6</v>
+        <v>0.95</v>
       </c>
       <c r="F19">
-        <v>3110.69</v>
+        <v>339.25</v>
       </c>
       <c r="G19">
-        <v>3731</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B20">
-        <v>2925</v>
+        <v>44403</v>
       </c>
       <c r="C20">
-        <v>35.23</v>
+        <v>163.67</v>
       </c>
       <c r="D20">
-        <v>58.73</v>
+        <v>293.29</v>
       </c>
       <c r="E20">
-        <v>19.51</v>
+        <v>20.51</v>
       </c>
       <c r="F20">
-        <v>344.08</v>
+        <v>2139.32</v>
       </c>
       <c r="G20">
-        <v>51</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B21">
-        <v>141837.28</v>
+        <v>339078.88</v>
       </c>
       <c r="C21">
-        <v>81.11</v>
+        <v>29.02</v>
       </c>
       <c r="D21">
-        <v>184.62</v>
+        <v>52.42</v>
       </c>
       <c r="E21">
-        <v>18.44</v>
+        <v>1.43</v>
       </c>
       <c r="F21">
-        <v>2839.88</v>
+        <v>705.6799999999999</v>
       </c>
       <c r="G21">
-        <v>1110</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Physician Office Based Coding Specialist</t>
         </is>
       </c>
       <c r="B22">
-        <v>405048</v>
+        <v>23152.05</v>
       </c>
       <c r="C22">
-        <v>104.1</v>
+        <v>18.13</v>
       </c>
       <c r="D22">
-        <v>245.03</v>
+        <v>41.97</v>
       </c>
       <c r="E22">
-        <v>21.01</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>6136.2</v>
+        <v>425.63</v>
       </c>
       <c r="G22">
-        <v>2502</v>
+        <v>899</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B23">
-        <v>308</v>
+        <v>33087</v>
       </c>
       <c r="C23">
-        <v>155.17</v>
+        <v>320.12</v>
       </c>
       <c r="D23">
-        <v>84.36</v>
+        <v>303.7</v>
       </c>
       <c r="E23">
-        <v>72.39</v>
+        <v>20.51</v>
       </c>
       <c r="F23">
-        <v>191.7</v>
+        <v>1750.35</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Professional Behavioral Health Counselor</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>14719</v>
+      </c>
+      <c r="C24">
+        <v>302.37</v>
+      </c>
+      <c r="D24">
+        <v>405.47</v>
+      </c>
+      <c r="E24">
+        <v>20.51</v>
+      </c>
+      <c r="F24">
+        <v>1887.29</v>
+      </c>
+      <c r="G24">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Radiography Technologist</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>103.72</v>
+      </c>
+      <c r="C25">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="D25">
+        <v>4.64</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>13.87</v>
+      </c>
+      <c r="G25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Registered Community Health Nurse</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1387977.9</v>
+      </c>
+      <c r="C26">
+        <v>244.13</v>
+      </c>
+      <c r="D26">
+        <v>599.21</v>
+      </c>
+      <c r="E26">
+        <v>9.6</v>
+      </c>
+      <c r="F26">
+        <v>14241.9</v>
+      </c>
+      <c r="G26">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Registered Dietitian</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>14196</v>
+      </c>
+      <c r="C27">
+        <v>170.98</v>
+      </c>
+      <c r="D27">
+        <v>687.95</v>
+      </c>
+      <c r="E27">
+        <v>19.51</v>
+      </c>
+      <c r="F27">
+        <v>4885.88</v>
+      </c>
+      <c r="G27">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Registered General Practice Nurse</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>1387115.52</v>
+      </c>
+      <c r="C28">
+        <v>793.2</v>
+      </c>
+      <c r="D28">
+        <v>1718.99</v>
+      </c>
+      <c r="E28">
+        <v>36.89</v>
+      </c>
+      <c r="F28">
+        <v>23770.81</v>
+      </c>
+      <c r="G28">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Registered Nurse</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2028936</v>
+      </c>
+      <c r="C29">
+        <v>521.45</v>
+      </c>
+      <c r="D29">
+        <v>934.38</v>
+      </c>
+      <c r="E29">
+        <v>21.01</v>
+      </c>
+      <c r="F29">
+        <v>13976.9</v>
+      </c>
+      <c r="G29">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Registered Record Administrator</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>410082.91</v>
+      </c>
+      <c r="C30">
+        <v>21.17</v>
+      </c>
+      <c r="D30">
+        <v>43.84</v>
+      </c>
+      <c r="E30">
+        <v>0.64</v>
+      </c>
+      <c r="F30">
+        <v>661.14</v>
+      </c>
+      <c r="G30">
+        <v>13774</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>704</v>
+      </c>
+      <c r="C31">
+        <v>354.67</v>
+      </c>
+      <c r="D31">
+        <v>287.7</v>
+      </c>
+      <c r="E31">
+        <v>72.39</v>
+      </c>
+      <c r="F31">
+        <v>479.25</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B24">
-        <v>17333.39</v>
-      </c>
-      <c r="C24">
-        <v>63.14</v>
-      </c>
-      <c r="D24">
-        <v>119.82</v>
-      </c>
-      <c r="E24">
+      <c r="B32">
+        <v>67521.3</v>
+      </c>
+      <c r="C32">
+        <v>245.96</v>
+      </c>
+      <c r="D32">
+        <v>395.04</v>
+      </c>
+      <c r="E32">
         <v>14.63</v>
       </c>
-      <c r="F24">
-        <v>1011.43</v>
-      </c>
-      <c r="G24">
+      <c r="F32">
+        <v>2669.06</v>
+      </c>
+      <c r="G32">
         <v>183</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>916.78</v>
+      </c>
+      <c r="C33">
+        <v>2.99</v>
+      </c>
+      <c r="D33">
+        <v>10.98</v>
+      </c>
+      <c r="E33">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F33">
+        <v>108.62</v>
+      </c>
+      <c r="G33">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Surgical Physician Assistant</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1539.49</v>
+      </c>
+      <c r="C34">
+        <v>6.84</v>
+      </c>
+      <c r="D34">
+        <v>11.6</v>
+      </c>
+      <c r="E34">
+        <v>0.48</v>
+      </c>
+      <c r="F34">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="G34">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1023,19 +1273,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>572</v>
+        <v>786.5</v>
       </c>
       <c r="C2">
-        <v>71.55</v>
+        <v>98.38</v>
       </c>
       <c r="D2">
-        <v>50.59</v>
+        <v>84.53</v>
       </c>
       <c r="E2">
         <v>35.77</v>
       </c>
       <c r="F2">
-        <v>143.1</v>
+        <v>214.65</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1044,576 +1294,819 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Case Manager / Care Coordinator</t>
         </is>
       </c>
       <c r="B3">
-        <v>317254.03</v>
+        <v>1283978.78</v>
       </c>
       <c r="C3">
-        <v>61.09</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="D3">
-        <v>114.75</v>
+        <v>180.76</v>
       </c>
       <c r="E3">
-        <v>13.38</v>
+        <v>2.63</v>
       </c>
       <c r="F3">
-        <v>1594.9</v>
+        <v>2704.94</v>
       </c>
       <c r="G3">
-        <v>3427</v>
+        <v>11466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B4">
-        <v>1801842</v>
+        <v>1353799.07</v>
       </c>
       <c r="C4">
-        <v>123.6</v>
+        <v>260.7</v>
       </c>
       <c r="D4">
-        <v>230.89</v>
+        <v>497.99</v>
       </c>
       <c r="E4">
-        <v>21.01</v>
+        <v>13.38</v>
       </c>
       <c r="F4">
-        <v>7830.88</v>
+        <v>6620.15</v>
       </c>
       <c r="G4">
-        <v>9405</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B5">
-        <v>708846.84</v>
+        <v>8912484</v>
       </c>
       <c r="C5">
-        <v>167.29</v>
+        <v>611.37</v>
       </c>
       <c r="D5">
-        <v>305.44</v>
+        <v>1088.62</v>
       </c>
       <c r="E5">
-        <v>15.87</v>
+        <v>21.01</v>
       </c>
       <c r="F5">
-        <v>2457.58</v>
+        <v>23412.33</v>
       </c>
       <c r="G5">
-        <v>2879</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B6">
-        <v>2407.09</v>
+        <v>150858.91</v>
       </c>
       <c r="C6">
-        <v>59.3</v>
+        <v>35.6</v>
       </c>
       <c r="D6">
-        <v>104.19</v>
+        <v>88.27</v>
       </c>
       <c r="E6">
-        <v>13.38</v>
+        <v>1.27</v>
       </c>
       <c r="F6">
-        <v>375.72</v>
+        <v>2407.93</v>
       </c>
       <c r="G6">
-        <v>29</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B7">
-        <v>13688724</v>
+        <v>10243.49</v>
       </c>
       <c r="C7">
-        <v>471.45</v>
+        <v>252.34</v>
       </c>
       <c r="D7">
-        <v>531.6</v>
+        <v>438.39</v>
       </c>
       <c r="E7">
-        <v>21.01</v>
+        <v>13.38</v>
       </c>
       <c r="F7">
-        <v>6976.78</v>
+        <v>2254.33</v>
       </c>
       <c r="G7">
-        <v>21658</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B8">
-        <v>2703</v>
+        <v>38198328</v>
       </c>
       <c r="C8">
-        <v>178.95</v>
+        <v>1315.59</v>
       </c>
       <c r="D8">
-        <v>270.76</v>
+        <v>1692.52</v>
       </c>
       <c r="E8">
-        <v>26.52</v>
+        <v>21.01</v>
       </c>
       <c r="F8">
-        <v>1032.44</v>
+        <v>29573.95</v>
       </c>
       <c r="G8">
-        <v>13</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>Health Information Technician</t>
         </is>
       </c>
       <c r="B9">
-        <v>704057.33</v>
+        <v>95799.45</v>
       </c>
       <c r="C9">
-        <v>96.95</v>
+        <v>28.07</v>
       </c>
       <c r="D9">
-        <v>186.79</v>
+        <v>47.88</v>
       </c>
       <c r="E9">
-        <v>9.6</v>
+        <v>0.64</v>
       </c>
       <c r="F9">
-        <v>2164.59</v>
+        <v>406.76</v>
       </c>
       <c r="G9">
-        <v>4954</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B10">
-        <v>95.16</v>
+        <v>6996</v>
       </c>
       <c r="C10">
-        <v>15.87</v>
+        <v>463.17</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>696.08</v>
       </c>
       <c r="E10">
-        <v>15.87</v>
+        <v>26.52</v>
       </c>
       <c r="F10">
-        <v>15.87</v>
+        <v>2581.1</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B11">
-        <v>1531076.28</v>
+        <v>2318108.34</v>
       </c>
       <c r="C11">
-        <v>129.54</v>
+        <v>319.22</v>
       </c>
       <c r="D11">
-        <v>250.23</v>
+        <v>670.22</v>
       </c>
       <c r="E11">
-        <v>24.71</v>
+        <v>9.6</v>
       </c>
       <c r="F11">
-        <v>3519.23</v>
+        <v>9143.24</v>
       </c>
       <c r="G11">
-        <v>7891</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>126.88</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>21.16</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>9.16</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>15.87</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>31.74</v>
       </c>
       <c r="G12">
-        <v>621</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B13">
-        <v>36779.83</v>
+        <v>4332255.54</v>
       </c>
       <c r="C13">
-        <v>38.6</v>
+        <v>366.54</v>
       </c>
       <c r="D13">
-        <v>80.91</v>
+        <v>817.64</v>
       </c>
       <c r="E13">
-        <v>9.6</v>
+        <v>24.71</v>
       </c>
       <c r="F13">
-        <v>855.05</v>
+        <v>20722.26</v>
       </c>
       <c r="G13">
-        <v>616</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B14">
-        <v>11076</v>
+        <v>191424.05</v>
       </c>
       <c r="C14">
-        <v>38.66</v>
+        <v>200.92</v>
       </c>
       <c r="D14">
-        <v>76.81999999999999</v>
+        <v>387.43</v>
       </c>
       <c r="E14">
-        <v>13.01</v>
+        <v>9.6</v>
       </c>
       <c r="F14">
-        <v>575.55</v>
+        <v>3580.29</v>
       </c>
       <c r="G14">
-        <v>220</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Other Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>36564</v>
+        <v>1057899.82</v>
       </c>
       <c r="C15">
-        <v>21.5</v>
+        <v>54.6</v>
       </c>
       <c r="D15">
-        <v>41.68</v>
+        <v>118.88</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="F15">
-        <v>483.93</v>
+        <v>3255.32</v>
       </c>
       <c r="G15">
-        <v>1125</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B16">
-        <v>19188</v>
+        <v>55900</v>
       </c>
       <c r="C16">
-        <v>70.73</v>
+        <v>195.12</v>
       </c>
       <c r="D16">
-        <v>114.89</v>
+        <v>492.29</v>
       </c>
       <c r="E16">
-        <v>20.51</v>
+        <v>13.01</v>
       </c>
       <c r="F16">
-        <v>981.98</v>
+        <v>2984.61</v>
       </c>
       <c r="G16">
-        <v>175</v>
+        <v>220</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="B17">
-        <v>1191456</v>
+        <v>23296.73</v>
       </c>
       <c r="C17">
-        <v>101.96</v>
+        <v>6.69</v>
       </c>
       <c r="D17">
-        <v>170.23</v>
+        <v>13.79</v>
       </c>
       <c r="E17">
-        <v>21.01</v>
+        <v>0.82</v>
       </c>
       <c r="F17">
-        <v>3334.89</v>
+        <v>200.72</v>
       </c>
       <c r="G17">
-        <v>7644</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B18">
-        <v>4592</v>
+        <v>116364</v>
       </c>
       <c r="C18">
-        <v>44.43</v>
+        <v>68.42</v>
       </c>
       <c r="D18">
-        <v>47.7</v>
+        <v>141.43</v>
       </c>
       <c r="E18">
-        <v>20.51</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>225.65</v>
+        <v>1603.54</v>
       </c>
       <c r="G18">
-        <v>61</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Phlebotomist</t>
         </is>
       </c>
       <c r="B19">
-        <v>5781</v>
+        <v>34036.34</v>
       </c>
       <c r="C19">
-        <v>118.76</v>
+        <v>11.62</v>
       </c>
       <c r="D19">
-        <v>130.9</v>
+        <v>24.28</v>
       </c>
       <c r="E19">
-        <v>20.51</v>
+        <v>0.95</v>
       </c>
       <c r="F19">
-        <v>615.42</v>
+        <v>339.25</v>
       </c>
       <c r="G19">
-        <v>29</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Registered Community Health Nurse</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B20">
-        <v>291723.95</v>
+        <v>44403</v>
       </c>
       <c r="C20">
-        <v>51.31</v>
+        <v>163.67</v>
       </c>
       <c r="D20">
-        <v>114.35</v>
+        <v>293.29</v>
       </c>
       <c r="E20">
-        <v>9.6</v>
+        <v>20.51</v>
       </c>
       <c r="F20">
-        <v>3110.69</v>
+        <v>2139.32</v>
       </c>
       <c r="G20">
-        <v>3731</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Registered Dietitian</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B21">
-        <v>2925</v>
+        <v>339078.88</v>
       </c>
       <c r="C21">
-        <v>35.23</v>
+        <v>29.02</v>
       </c>
       <c r="D21">
-        <v>58.73</v>
+        <v>52.42</v>
       </c>
       <c r="E21">
-        <v>19.51</v>
+        <v>1.43</v>
       </c>
       <c r="F21">
-        <v>344.08</v>
+        <v>705.6799999999999</v>
       </c>
       <c r="G21">
-        <v>51</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Registered General Practice Nurse</t>
+          <t>Physician Office Based Coding Specialist</t>
         </is>
       </c>
       <c r="B22">
-        <v>141837.28</v>
+        <v>23417.34</v>
       </c>
       <c r="C22">
-        <v>81.11</v>
+        <v>18.2</v>
       </c>
       <c r="D22">
-        <v>184.62</v>
+        <v>42.43</v>
       </c>
       <c r="E22">
-        <v>18.44</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>2839.88</v>
+        <v>425.63</v>
       </c>
       <c r="G22">
-        <v>1110</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Registered Nurse</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B23">
-        <v>405048</v>
+        <v>33087</v>
       </c>
       <c r="C23">
-        <v>104.1</v>
+        <v>320.12</v>
       </c>
       <c r="D23">
-        <v>245.03</v>
+        <v>303.7</v>
       </c>
       <c r="E23">
-        <v>21.01</v>
+        <v>20.51</v>
       </c>
       <c r="F23">
-        <v>6136.2</v>
+        <v>1750.35</v>
       </c>
       <c r="G23">
-        <v>2502</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B24">
-        <v>308</v>
+        <v>14719</v>
       </c>
       <c r="C24">
-        <v>155.17</v>
+        <v>302.37</v>
       </c>
       <c r="D24">
-        <v>84.36</v>
+        <v>405.47</v>
       </c>
       <c r="E24">
-        <v>72.39</v>
+        <v>20.51</v>
       </c>
       <c r="F24">
-        <v>191.7</v>
+        <v>1887.29</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Radiography Technologist</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>103.72</v>
+      </c>
+      <c r="C25">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="D25">
+        <v>4.64</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>13.87</v>
+      </c>
+      <c r="G25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Registered Community Health Nurse</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1387977.9</v>
+      </c>
+      <c r="C26">
+        <v>244.13</v>
+      </c>
+      <c r="D26">
+        <v>599.21</v>
+      </c>
+      <c r="E26">
+        <v>9.6</v>
+      </c>
+      <c r="F26">
+        <v>14241.9</v>
+      </c>
+      <c r="G26">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Registered Dietitian</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>14196</v>
+      </c>
+      <c r="C27">
+        <v>170.98</v>
+      </c>
+      <c r="D27">
+        <v>687.95</v>
+      </c>
+      <c r="E27">
+        <v>19.51</v>
+      </c>
+      <c r="F27">
+        <v>4885.88</v>
+      </c>
+      <c r="G27">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Registered General Practice Nurse</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>1387115.52</v>
+      </c>
+      <c r="C28">
+        <v>793.2</v>
+      </c>
+      <c r="D28">
+        <v>1718.99</v>
+      </c>
+      <c r="E28">
+        <v>36.89</v>
+      </c>
+      <c r="F28">
+        <v>23770.81</v>
+      </c>
+      <c r="G28">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Registered Nurse</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2028936</v>
+      </c>
+      <c r="C29">
+        <v>521.45</v>
+      </c>
+      <c r="D29">
+        <v>934.38</v>
+      </c>
+      <c r="E29">
+        <v>21.01</v>
+      </c>
+      <c r="F29">
+        <v>13976.9</v>
+      </c>
+      <c r="G29">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Registered Record Administrator</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>414374.55</v>
+      </c>
+      <c r="C30">
+        <v>21.24</v>
+      </c>
+      <c r="D30">
+        <v>44.56</v>
+      </c>
+      <c r="E30">
+        <v>0.64</v>
+      </c>
+      <c r="F30">
+        <v>661.14</v>
+      </c>
+      <c r="G30">
+        <v>14045</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>704</v>
+      </c>
+      <c r="C31">
+        <v>354.67</v>
+      </c>
+      <c r="D31">
+        <v>287.7</v>
+      </c>
+      <c r="E31">
+        <v>72.39</v>
+      </c>
+      <c r="F31">
+        <v>479.25</v>
+      </c>
+      <c r="G31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Specialist</t>
         </is>
       </c>
-      <c r="B25">
-        <v>17333.39</v>
-      </c>
-      <c r="C25">
-        <v>63.14</v>
-      </c>
-      <c r="D25">
-        <v>119.82</v>
-      </c>
-      <c r="E25">
+      <c r="B32">
+        <v>67521.3</v>
+      </c>
+      <c r="C32">
+        <v>245.96</v>
+      </c>
+      <c r="D32">
+        <v>395.04</v>
+      </c>
+      <c r="E32">
         <v>14.63</v>
       </c>
-      <c r="F25">
-        <v>1011.43</v>
-      </c>
-      <c r="G25">
+      <c r="F32">
+        <v>2669.06</v>
+      </c>
+      <c r="G32">
         <v>183</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>919.03</v>
+      </c>
+      <c r="C33">
+        <v>2.98</v>
+      </c>
+      <c r="D33">
+        <v>10.95</v>
+      </c>
+      <c r="E33">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F33">
+        <v>108.62</v>
+      </c>
+      <c r="G33">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Surgical Physician Assistant</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1539.49</v>
+      </c>
+      <c r="C34">
+        <v>6.84</v>
+      </c>
+      <c r="D34">
+        <v>11.6</v>
+      </c>
+      <c r="E34">
+        <v>0.48</v>
+      </c>
+      <c r="F34">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="G34">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +2116,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1666,100 +2159,125 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Administrative Non-clinical</t>
         </is>
       </c>
       <c r="B2">
-        <v>16682022</v>
+        <v>2858338.71</v>
       </c>
       <c r="C2">
-        <v>570.11</v>
+        <v>99.59</v>
       </c>
       <c r="D2">
-        <v>615.84</v>
+        <v>193.06</v>
       </c>
       <c r="E2">
-        <v>21.01</v>
+        <v>0.64</v>
       </c>
       <c r="F2">
-        <v>9557.690000000001</v>
+        <v>4937.01</v>
       </c>
       <c r="G2">
-        <v>21900</v>
+        <v>21325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>1192853.87</v>
+        <v>43187508</v>
       </c>
       <c r="C3">
-        <v>84.59</v>
+        <v>1481.79</v>
       </c>
       <c r="D3">
-        <v>189.85</v>
+        <v>1823.64</v>
       </c>
       <c r="E3">
-        <v>9.6</v>
+        <v>21.01</v>
       </c>
       <c r="F3">
-        <v>6136.2</v>
+        <v>32699.49</v>
       </c>
       <c r="G3">
-        <v>9362</v>
+        <v>21774</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B4">
-        <v>1524367.08</v>
+        <v>15169330.1</v>
       </c>
       <c r="C4">
-        <v>122.12</v>
+        <v>645.67</v>
       </c>
       <c r="D4">
-        <v>241.63</v>
+        <v>1186.83</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="F4">
-        <v>2457.58</v>
+        <v>26899.89</v>
       </c>
       <c r="G4">
-        <v>8547</v>
+        <v>15613</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3692413.82</v>
+      </c>
+      <c r="C5">
+        <v>171.15</v>
+      </c>
+      <c r="D5">
+        <v>534.72</v>
+      </c>
+      <c r="E5">
+        <v>0.48</v>
+      </c>
+      <c r="F5">
+        <v>9143.24</v>
+      </c>
+      <c r="G5">
+        <v>14899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Uncategorised</t>
         </is>
       </c>
-      <c r="B5">
-        <v>1531076.28</v>
-      </c>
-      <c r="C5">
-        <v>129.54</v>
-      </c>
-      <c r="D5">
-        <v>250.23</v>
-      </c>
-      <c r="E5">
+      <c r="B6">
+        <v>4332255.54</v>
+      </c>
+      <c r="C6">
+        <v>366.54</v>
+      </c>
+      <c r="D6">
+        <v>817.64</v>
+      </c>
+      <c r="E6">
         <v>24.71</v>
       </c>
-      <c r="F5">
-        <v>3519.23</v>
-      </c>
-      <c r="G5">
+      <c r="F6">
+        <v>20722.26</v>
+      </c>
+      <c r="G6">
         <v>7891</v>
       </c>
     </row>
@@ -1770,7 +2288,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1813,51 +2331,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Administrative Non-clinical</t>
         </is>
       </c>
       <c r="B2">
-        <v>16682022</v>
+        <v>2879093.27</v>
       </c>
       <c r="C2">
-        <v>570.11</v>
+        <v>99.52</v>
       </c>
       <c r="D2">
-        <v>615.84</v>
+        <v>194.09</v>
       </c>
       <c r="E2">
-        <v>21.01</v>
+        <v>0.64</v>
       </c>
       <c r="F2">
-        <v>9557.690000000001</v>
+        <v>4937.01</v>
       </c>
       <c r="G2">
-        <v>21900</v>
+        <v>21822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>43187508</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1481.79</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1823.64</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>21.01</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>32699.49</v>
       </c>
       <c r="G3">
-        <v>621</v>
+        <v>21774</v>
       </c>
     </row>
     <row r="4">
@@ -1867,22 +2385,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>1192853.87</v>
+        <v>15169330.1</v>
       </c>
       <c r="C4">
-        <v>84.59</v>
+        <v>645.67</v>
       </c>
       <c r="D4">
-        <v>189.85</v>
+        <v>1186.83</v>
       </c>
       <c r="E4">
         <v>9.6</v>
       </c>
       <c r="F4">
-        <v>6136.2</v>
+        <v>26899.89</v>
       </c>
       <c r="G4">
-        <v>9362</v>
+        <v>15613</v>
       </c>
     </row>
     <row r="5">
@@ -1892,22 +2410,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>1524367.08</v>
+        <v>3692413.82</v>
       </c>
       <c r="C5">
-        <v>122.12</v>
+        <v>171.15</v>
       </c>
       <c r="D5">
-        <v>241.63</v>
+        <v>534.72</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0.48</v>
       </c>
       <c r="F5">
-        <v>2457.58</v>
+        <v>9143.24</v>
       </c>
       <c r="G5">
-        <v>8547</v>
+        <v>14899</v>
       </c>
     </row>
     <row r="6">
@@ -1917,22 +2435,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>1531076.28</v>
+        <v>4332255.54</v>
       </c>
       <c r="C6">
-        <v>129.54</v>
+        <v>366.54</v>
       </c>
       <c r="D6">
-        <v>250.23</v>
+        <v>817.64</v>
       </c>
       <c r="E6">
         <v>24.71</v>
       </c>
       <c r="F6">
-        <v>3519.23</v>
+        <v>20722.26</v>
       </c>
       <c r="G6">
         <v>7891</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_costs_OMOP.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,19 +401,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>786.5</v>
+        <v>572</v>
       </c>
       <c r="C2">
-        <v>98.38</v>
+        <v>71.55</v>
       </c>
       <c r="D2">
-        <v>84.53</v>
+        <v>50.59</v>
       </c>
       <c r="E2">
         <v>35.77</v>
       </c>
       <c r="F2">
-        <v>214.65</v>
+        <v>143.1</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -422,801 +422,551 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Case Manager / Care Coordinator</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B3">
-        <v>1273077.56</v>
+        <v>317254.03</v>
       </c>
       <c r="C3">
-        <v>79.55</v>
+        <v>61.09</v>
       </c>
       <c r="D3">
-        <v>178.25</v>
+        <v>114.75</v>
       </c>
       <c r="E3">
-        <v>2.63</v>
+        <v>13.38</v>
       </c>
       <c r="F3">
-        <v>2704.94</v>
+        <v>1594.9</v>
       </c>
       <c r="G3">
-        <v>11268</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B4">
-        <v>1353799.07</v>
+        <v>1801842</v>
       </c>
       <c r="C4">
-        <v>260.7</v>
+        <v>123.6</v>
       </c>
       <c r="D4">
-        <v>497.99</v>
+        <v>230.89</v>
       </c>
       <c r="E4">
-        <v>13.38</v>
+        <v>21.01</v>
       </c>
       <c r="F4">
-        <v>6620.15</v>
+        <v>7830.88</v>
       </c>
       <c r="G4">
-        <v>3427</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B5">
-        <v>8912484</v>
+        <v>708846.84</v>
       </c>
       <c r="C5">
-        <v>611.37</v>
+        <v>167.29</v>
       </c>
       <c r="D5">
-        <v>1088.62</v>
+        <v>305.44</v>
       </c>
       <c r="E5">
-        <v>21.01</v>
+        <v>15.87</v>
       </c>
       <c r="F5">
-        <v>23412.33</v>
+        <v>2457.58</v>
       </c>
       <c r="G5">
-        <v>9405</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B6">
-        <v>150858.91</v>
+        <v>2407.09</v>
       </c>
       <c r="C6">
-        <v>35.6</v>
+        <v>59.3</v>
       </c>
       <c r="D6">
-        <v>88.27</v>
+        <v>104.19</v>
       </c>
       <c r="E6">
-        <v>1.27</v>
+        <v>13.38</v>
       </c>
       <c r="F6">
-        <v>2407.93</v>
+        <v>375.72</v>
       </c>
       <c r="G6">
-        <v>2879</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B7">
-        <v>10243.49</v>
+        <v>13688724</v>
       </c>
       <c r="C7">
-        <v>252.34</v>
+        <v>471.45</v>
       </c>
       <c r="D7">
-        <v>438.39</v>
+        <v>531.6</v>
       </c>
       <c r="E7">
-        <v>13.38</v>
+        <v>21.01</v>
       </c>
       <c r="F7">
-        <v>2254.33</v>
+        <v>6976.78</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B8">
-        <v>38198328</v>
+        <v>2703</v>
       </c>
       <c r="C8">
-        <v>1315.59</v>
+        <v>178.95</v>
       </c>
       <c r="D8">
-        <v>1692.52</v>
+        <v>270.76</v>
       </c>
       <c r="E8">
-        <v>21.01</v>
+        <v>26.52</v>
       </c>
       <c r="F8">
-        <v>29573.95</v>
+        <v>1032.44</v>
       </c>
       <c r="G8">
-        <v>21658</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Health Information Technician</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B9">
-        <v>94819.45</v>
+        <v>704057.33</v>
       </c>
       <c r="C9">
-        <v>28.02</v>
+        <v>96.95</v>
       </c>
       <c r="D9">
-        <v>47.42</v>
+        <v>186.79</v>
       </c>
       <c r="E9">
-        <v>0.64</v>
+        <v>9.6</v>
       </c>
       <c r="F9">
-        <v>406.76</v>
+        <v>2164.59</v>
       </c>
       <c r="G9">
-        <v>2422</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B10">
-        <v>6996</v>
+        <v>95.16</v>
       </c>
       <c r="C10">
-        <v>463.17</v>
+        <v>15.87</v>
       </c>
       <c r="D10">
-        <v>696.08</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>26.52</v>
+        <v>15.87</v>
       </c>
       <c r="F10">
-        <v>2581.1</v>
+        <v>15.87</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>2318108.34</v>
+        <v>1531076.28</v>
       </c>
       <c r="C11">
-        <v>319.22</v>
+        <v>129.54</v>
       </c>
       <c r="D11">
-        <v>670.22</v>
+        <v>250.23</v>
       </c>
       <c r="E11">
-        <v>9.6</v>
+        <v>24.71</v>
       </c>
       <c r="F11">
-        <v>9143.24</v>
+        <v>3519.23</v>
       </c>
       <c r="G11">
-        <v>4954</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B12">
-        <v>126.88</v>
+        <v>36779.83</v>
       </c>
       <c r="C12">
-        <v>21.16</v>
+        <v>38.6</v>
       </c>
       <c r="D12">
-        <v>9.16</v>
+        <v>80.91</v>
       </c>
       <c r="E12">
-        <v>15.87</v>
+        <v>9.6</v>
       </c>
       <c r="F12">
-        <v>31.74</v>
+        <v>855.05</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B13">
-        <v>4332255.54</v>
+        <v>11076</v>
       </c>
       <c r="C13">
-        <v>366.54</v>
+        <v>38.66</v>
       </c>
       <c r="D13">
-        <v>817.64</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="E13">
-        <v>24.71</v>
+        <v>13.01</v>
       </c>
       <c r="F13">
-        <v>20722.26</v>
+        <v>575.55</v>
       </c>
       <c r="G13">
-        <v>7891</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B14">
-        <v>191424.05</v>
+        <v>36564</v>
       </c>
       <c r="C14">
-        <v>200.92</v>
+        <v>21.5</v>
       </c>
       <c r="D14">
-        <v>387.43</v>
+        <v>41.68</v>
       </c>
       <c r="E14">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>3580.29</v>
+        <v>483.93</v>
       </c>
       <c r="G14">
-        <v>616</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Other Technician</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B15">
-        <v>1053829.64</v>
+        <v>19188</v>
       </c>
       <c r="C15">
-        <v>54.61</v>
+        <v>70.73</v>
       </c>
       <c r="D15">
-        <v>118.58</v>
+        <v>114.89</v>
       </c>
       <c r="E15">
-        <v>1.91</v>
+        <v>20.51</v>
       </c>
       <c r="F15">
-        <v>3255.32</v>
+        <v>981.98</v>
       </c>
       <c r="G15">
-        <v>13599</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B16">
-        <v>55900</v>
+        <v>1191456</v>
       </c>
       <c r="C16">
-        <v>195.12</v>
+        <v>101.96</v>
       </c>
       <c r="D16">
-        <v>492.29</v>
+        <v>170.23</v>
       </c>
       <c r="E16">
-        <v>13.01</v>
+        <v>21.01</v>
       </c>
       <c r="F16">
-        <v>2984.61</v>
+        <v>3334.89</v>
       </c>
       <c r="G16">
-        <v>220</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B17">
-        <v>23296.73</v>
+        <v>4592</v>
       </c>
       <c r="C17">
-        <v>6.69</v>
+        <v>44.43</v>
       </c>
       <c r="D17">
-        <v>13.79</v>
+        <v>47.7</v>
       </c>
       <c r="E17">
-        <v>0.82</v>
+        <v>20.51</v>
       </c>
       <c r="F17">
-        <v>200.72</v>
+        <v>225.65</v>
       </c>
       <c r="G17">
-        <v>2410</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B18">
-        <v>116364</v>
+        <v>5781</v>
       </c>
       <c r="C18">
-        <v>68.42</v>
+        <v>118.76</v>
       </c>
       <c r="D18">
-        <v>141.43</v>
+        <v>130.9</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>20.51</v>
       </c>
       <c r="F18">
-        <v>1603.54</v>
+        <v>615.42</v>
       </c>
       <c r="G18">
-        <v>1125</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B19">
-        <v>34036.34</v>
+        <v>291723.95</v>
       </c>
       <c r="C19">
-        <v>11.62</v>
+        <v>51.31</v>
       </c>
       <c r="D19">
-        <v>24.28</v>
+        <v>114.35</v>
       </c>
       <c r="E19">
-        <v>0.95</v>
+        <v>9.6</v>
       </c>
       <c r="F19">
-        <v>339.25</v>
+        <v>3110.69</v>
       </c>
       <c r="G19">
-        <v>1877</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B20">
-        <v>44403</v>
+        <v>2925</v>
       </c>
       <c r="C20">
-        <v>163.67</v>
+        <v>35.23</v>
       </c>
       <c r="D20">
-        <v>293.29</v>
+        <v>58.73</v>
       </c>
       <c r="E20">
-        <v>20.51</v>
+        <v>19.51</v>
       </c>
       <c r="F20">
-        <v>2139.32</v>
+        <v>344.08</v>
       </c>
       <c r="G20">
-        <v>175</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B21">
-        <v>339078.88</v>
+        <v>141837.28</v>
       </c>
       <c r="C21">
-        <v>29.02</v>
+        <v>81.11</v>
       </c>
       <c r="D21">
-        <v>52.42</v>
+        <v>184.62</v>
       </c>
       <c r="E21">
-        <v>1.43</v>
+        <v>18.44</v>
       </c>
       <c r="F21">
-        <v>705.6799999999999</v>
+        <v>2839.88</v>
       </c>
       <c r="G21">
-        <v>7644</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Physician Office Based Coding Specialist</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>23152.05</v>
+        <v>405048</v>
       </c>
       <c r="C22">
-        <v>18.13</v>
+        <v>104.1</v>
       </c>
       <c r="D22">
-        <v>41.97</v>
+        <v>245.03</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>21.01</v>
       </c>
       <c r="F22">
-        <v>425.63</v>
+        <v>6136.2</v>
       </c>
       <c r="G22">
-        <v>899</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B23">
-        <v>33087</v>
+        <v>308</v>
       </c>
       <c r="C23">
-        <v>320.12</v>
+        <v>155.17</v>
       </c>
       <c r="D23">
-        <v>303.7</v>
+        <v>84.36</v>
       </c>
       <c r="E23">
-        <v>20.51</v>
+        <v>72.39</v>
       </c>
       <c r="F23">
-        <v>1750.35</v>
+        <v>191.7</v>
       </c>
       <c r="G23">
-        <v>61</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="B24">
-        <v>14719</v>
+        <v>17333.39</v>
       </c>
       <c r="C24">
-        <v>302.37</v>
+        <v>63.14</v>
       </c>
       <c r="D24">
-        <v>405.47</v>
+        <v>119.82</v>
       </c>
       <c r="E24">
-        <v>20.51</v>
+        <v>14.63</v>
       </c>
       <c r="F24">
-        <v>1887.29</v>
+        <v>1011.43</v>
       </c>
       <c r="G24">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Radiography Technologist</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>103.72</v>
-      </c>
-      <c r="C25">
-        <v>8.390000000000001</v>
-      </c>
-      <c r="D25">
-        <v>4.64</v>
-      </c>
-      <c r="E25">
-        <v>2</v>
-      </c>
-      <c r="F25">
-        <v>13.87</v>
-      </c>
-      <c r="G25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Registered Community Health Nurse</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>1387977.9</v>
-      </c>
-      <c r="C26">
-        <v>244.13</v>
-      </c>
-      <c r="D26">
-        <v>599.21</v>
-      </c>
-      <c r="E26">
-        <v>9.6</v>
-      </c>
-      <c r="F26">
-        <v>14241.9</v>
-      </c>
-      <c r="G26">
-        <v>3731</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Registered Dietitian</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>14196</v>
-      </c>
-      <c r="C27">
-        <v>170.98</v>
-      </c>
-      <c r="D27">
-        <v>687.95</v>
-      </c>
-      <c r="E27">
-        <v>19.51</v>
-      </c>
-      <c r="F27">
-        <v>4885.88</v>
-      </c>
-      <c r="G27">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Registered General Practice Nurse</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>1387115.52</v>
-      </c>
-      <c r="C28">
-        <v>793.2</v>
-      </c>
-      <c r="D28">
-        <v>1718.99</v>
-      </c>
-      <c r="E28">
-        <v>36.89</v>
-      </c>
-      <c r="F28">
-        <v>23770.81</v>
-      </c>
-      <c r="G28">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Registered Nurse</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>2028936</v>
-      </c>
-      <c r="C29">
-        <v>521.45</v>
-      </c>
-      <c r="D29">
-        <v>934.38</v>
-      </c>
-      <c r="E29">
-        <v>21.01</v>
-      </c>
-      <c r="F29">
-        <v>13976.9</v>
-      </c>
-      <c r="G29">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Registered Record Administrator</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>410082.91</v>
-      </c>
-      <c r="C30">
-        <v>21.17</v>
-      </c>
-      <c r="D30">
-        <v>43.84</v>
-      </c>
-      <c r="E30">
-        <v>0.64</v>
-      </c>
-      <c r="F30">
-        <v>661.14</v>
-      </c>
-      <c r="G30">
-        <v>13774</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>704</v>
-      </c>
-      <c r="C31">
-        <v>354.67</v>
-      </c>
-      <c r="D31">
-        <v>287.7</v>
-      </c>
-      <c r="E31">
-        <v>72.39</v>
-      </c>
-      <c r="F31">
-        <v>479.25</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>67521.3</v>
-      </c>
-      <c r="C32">
-        <v>245.96</v>
-      </c>
-      <c r="D32">
-        <v>395.04</v>
-      </c>
-      <c r="E32">
-        <v>14.63</v>
-      </c>
-      <c r="F32">
-        <v>2669.06</v>
-      </c>
-      <c r="G32">
         <v>183</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>916.78</v>
-      </c>
-      <c r="C33">
-        <v>2.99</v>
-      </c>
-      <c r="D33">
-        <v>10.98</v>
-      </c>
-      <c r="E33">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F33">
-        <v>108.62</v>
-      </c>
-      <c r="G33">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Surgical Physician Assistant</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>1539.49</v>
-      </c>
-      <c r="C34">
-        <v>6.84</v>
-      </c>
-      <c r="D34">
-        <v>11.6</v>
-      </c>
-      <c r="E34">
-        <v>0.48</v>
-      </c>
-      <c r="F34">
-        <v>80.81999999999999</v>
-      </c>
-      <c r="G34">
-        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1273,19 +1023,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>786.5</v>
+        <v>572</v>
       </c>
       <c r="C2">
-        <v>98.38</v>
+        <v>71.55</v>
       </c>
       <c r="D2">
-        <v>84.53</v>
+        <v>50.59</v>
       </c>
       <c r="E2">
         <v>35.77</v>
       </c>
       <c r="F2">
-        <v>214.65</v>
+        <v>143.1</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1294,819 +1044,576 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Case Manager / Care Coordinator</t>
+          <t>Clinical Nurse Specialist</t>
         </is>
       </c>
       <c r="B3">
-        <v>1283978.78</v>
+        <v>317254.03</v>
       </c>
       <c r="C3">
-        <v>79.79000000000001</v>
+        <v>61.09</v>
       </c>
       <c r="D3">
-        <v>180.76</v>
+        <v>114.75</v>
       </c>
       <c r="E3">
-        <v>2.63</v>
+        <v>13.38</v>
       </c>
       <c r="F3">
-        <v>2704.94</v>
+        <v>1594.9</v>
       </c>
       <c r="G3">
-        <v>11466</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Clinical Nurse Specialist</t>
+          <t>Community Health Nurse Practitioner</t>
         </is>
       </c>
       <c r="B4">
-        <v>1353799.07</v>
+        <v>1801842</v>
       </c>
       <c r="C4">
-        <v>260.7</v>
+        <v>123.6</v>
       </c>
       <c r="D4">
-        <v>497.99</v>
+        <v>230.89</v>
       </c>
       <c r="E4">
-        <v>13.38</v>
+        <v>21.01</v>
       </c>
       <c r="F4">
-        <v>6620.15</v>
+        <v>7830.88</v>
       </c>
       <c r="G4">
-        <v>3427</v>
+        <v>9405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Community Health Nurse Practitioner</t>
+          <t>Community Health Worker</t>
         </is>
       </c>
       <c r="B5">
-        <v>8912484</v>
+        <v>708846.84</v>
       </c>
       <c r="C5">
-        <v>611.37</v>
+        <v>167.29</v>
       </c>
       <c r="D5">
-        <v>1088.62</v>
+        <v>305.44</v>
       </c>
       <c r="E5">
-        <v>21.01</v>
+        <v>15.87</v>
       </c>
       <c r="F5">
-        <v>23412.33</v>
+        <v>2457.58</v>
       </c>
       <c r="G5">
-        <v>9405</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Community Health Worker</t>
+          <t>Community Psych / Mental Health Nurse</t>
         </is>
       </c>
       <c r="B6">
-        <v>150858.91</v>
+        <v>2407.09</v>
       </c>
       <c r="C6">
-        <v>35.6</v>
+        <v>59.3</v>
       </c>
       <c r="D6">
-        <v>88.27</v>
+        <v>104.19</v>
       </c>
       <c r="E6">
-        <v>1.27</v>
+        <v>13.38</v>
       </c>
       <c r="F6">
-        <v>2407.93</v>
+        <v>375.72</v>
       </c>
       <c r="G6">
-        <v>2879</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Community Psych / Mental Health Nurse</t>
+          <t>General Practice</t>
         </is>
       </c>
       <c r="B7">
-        <v>10243.49</v>
+        <v>13688724</v>
       </c>
       <c r="C7">
-        <v>252.34</v>
+        <v>471.45</v>
       </c>
       <c r="D7">
-        <v>438.39</v>
+        <v>531.6</v>
       </c>
       <c r="E7">
-        <v>13.38</v>
+        <v>21.01</v>
       </c>
       <c r="F7">
-        <v>2254.33</v>
+        <v>6976.78</v>
       </c>
       <c r="G7">
-        <v>29</v>
+        <v>21658</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>General Practice</t>
+          <t>Marriage and Family Therapist</t>
         </is>
       </c>
       <c r="B8">
-        <v>38198328</v>
+        <v>2703</v>
       </c>
       <c r="C8">
-        <v>1315.59</v>
+        <v>178.95</v>
       </c>
       <c r="D8">
-        <v>1692.52</v>
+        <v>270.76</v>
       </c>
       <c r="E8">
-        <v>21.01</v>
+        <v>26.52</v>
       </c>
       <c r="F8">
-        <v>29573.95</v>
+        <v>1032.44</v>
       </c>
       <c r="G8">
-        <v>21658</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Health Information Technician</t>
+          <t>Medical Physician Assistant</t>
         </is>
       </c>
       <c r="B9">
-        <v>95799.45</v>
+        <v>704057.33</v>
       </c>
       <c r="C9">
-        <v>28.07</v>
+        <v>96.95</v>
       </c>
       <c r="D9">
-        <v>47.88</v>
+        <v>186.79</v>
       </c>
       <c r="E9">
-        <v>0.64</v>
+        <v>9.6</v>
       </c>
       <c r="F9">
-        <v>406.76</v>
+        <v>2164.59</v>
       </c>
       <c r="G9">
-        <v>2483</v>
+        <v>4954</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marriage and Family Therapist</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B10">
-        <v>6996</v>
+        <v>95.16</v>
       </c>
       <c r="C10">
-        <v>463.17</v>
+        <v>15.87</v>
       </c>
       <c r="D10">
-        <v>696.08</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>26.52</v>
+        <v>15.87</v>
       </c>
       <c r="F10">
-        <v>2581.1</v>
+        <v>15.87</v>
       </c>
       <c r="G10">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Medical Physician Assistant</t>
+          <t>No matching concept</t>
         </is>
       </c>
       <c r="B11">
-        <v>2318108.34</v>
+        <v>1531076.28</v>
       </c>
       <c r="C11">
-        <v>319.22</v>
+        <v>129.54</v>
       </c>
       <c r="D11">
-        <v>670.22</v>
+        <v>250.23</v>
       </c>
       <c r="E11">
-        <v>9.6</v>
+        <v>24.71</v>
       </c>
       <c r="F11">
-        <v>9143.24</v>
+        <v>3519.23</v>
       </c>
       <c r="G11">
-        <v>4954</v>
+        <v>7891</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B12">
-        <v>126.88</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>21.16</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>9.16</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>15.87</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>31.74</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>621</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>No matching concept</t>
+          <t>Nurse Practitioner</t>
         </is>
       </c>
       <c r="B13">
-        <v>4332255.54</v>
+        <v>36779.83</v>
       </c>
       <c r="C13">
-        <v>366.54</v>
+        <v>38.6</v>
       </c>
       <c r="D13">
-        <v>817.64</v>
+        <v>80.91</v>
       </c>
       <c r="E13">
-        <v>24.71</v>
+        <v>9.6</v>
       </c>
       <c r="F13">
-        <v>20722.26</v>
+        <v>855.05</v>
       </c>
       <c r="G13">
-        <v>7891</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nurse Practitioner</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B14">
-        <v>191424.05</v>
+        <v>11076</v>
       </c>
       <c r="C14">
-        <v>200.92</v>
+        <v>38.66</v>
       </c>
       <c r="D14">
-        <v>387.43</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="E14">
-        <v>9.6</v>
+        <v>13.01</v>
       </c>
       <c r="F14">
-        <v>3580.29</v>
+        <v>575.55</v>
       </c>
       <c r="G14">
-        <v>616</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Other Technician</t>
+          <t>Pharmacy Technician</t>
         </is>
       </c>
       <c r="B15">
-        <v>1057899.82</v>
+        <v>36564</v>
       </c>
       <c r="C15">
-        <v>54.6</v>
+        <v>21.5</v>
       </c>
       <c r="D15">
-        <v>118.88</v>
+        <v>41.68</v>
       </c>
       <c r="E15">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>3255.32</v>
+        <v>483.93</v>
       </c>
       <c r="G15">
-        <v>13746</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Physical Hand Therapist</t>
         </is>
       </c>
       <c r="B16">
-        <v>55900</v>
+        <v>19188</v>
       </c>
       <c r="C16">
-        <v>195.12</v>
+        <v>70.73</v>
       </c>
       <c r="D16">
-        <v>492.29</v>
+        <v>114.89</v>
       </c>
       <c r="E16">
-        <v>13.01</v>
+        <v>20.51</v>
       </c>
       <c r="F16">
-        <v>2984.61</v>
+        <v>981.98</v>
       </c>
       <c r="G16">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B17">
-        <v>23296.73</v>
+        <v>1191456</v>
       </c>
       <c r="C17">
-        <v>6.69</v>
+        <v>101.96</v>
       </c>
       <c r="D17">
-        <v>13.79</v>
+        <v>170.23</v>
       </c>
       <c r="E17">
-        <v>0.82</v>
+        <v>21.01</v>
       </c>
       <c r="F17">
-        <v>200.72</v>
+        <v>3334.89</v>
       </c>
       <c r="G17">
-        <v>2410</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pharmacy Technician</t>
+          <t>Podiatrist</t>
         </is>
       </c>
       <c r="B18">
-        <v>116364</v>
+        <v>4592</v>
       </c>
       <c r="C18">
-        <v>68.42</v>
+        <v>44.43</v>
       </c>
       <c r="D18">
-        <v>141.43</v>
+        <v>47.7</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>20.51</v>
       </c>
       <c r="F18">
-        <v>1603.54</v>
+        <v>225.65</v>
       </c>
       <c r="G18">
-        <v>1125</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Professional Behavioral Health Counselor</t>
         </is>
       </c>
       <c r="B19">
-        <v>34036.34</v>
+        <v>5781</v>
       </c>
       <c r="C19">
-        <v>11.62</v>
+        <v>118.76</v>
       </c>
       <c r="D19">
-        <v>24.28</v>
+        <v>130.9</v>
       </c>
       <c r="E19">
-        <v>0.95</v>
+        <v>20.51</v>
       </c>
       <c r="F19">
-        <v>339.25</v>
+        <v>615.42</v>
       </c>
       <c r="G19">
-        <v>1877</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Physical Hand Therapist</t>
+          <t>Registered Community Health Nurse</t>
         </is>
       </c>
       <c r="B20">
-        <v>44403</v>
+        <v>291723.95</v>
       </c>
       <c r="C20">
-        <v>163.67</v>
+        <v>51.31</v>
       </c>
       <c r="D20">
-        <v>293.29</v>
+        <v>114.35</v>
       </c>
       <c r="E20">
-        <v>20.51</v>
+        <v>9.6</v>
       </c>
       <c r="F20">
-        <v>2139.32</v>
+        <v>3110.69</v>
       </c>
       <c r="G20">
-        <v>175</v>
+        <v>3731</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Registered Dietitian</t>
         </is>
       </c>
       <c r="B21">
-        <v>339078.88</v>
+        <v>2925</v>
       </c>
       <c r="C21">
-        <v>29.02</v>
+        <v>35.23</v>
       </c>
       <c r="D21">
-        <v>52.42</v>
+        <v>58.73</v>
       </c>
       <c r="E21">
-        <v>1.43</v>
+        <v>19.51</v>
       </c>
       <c r="F21">
-        <v>705.6799999999999</v>
+        <v>344.08</v>
       </c>
       <c r="G21">
-        <v>7644</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Physician Office Based Coding Specialist</t>
+          <t>Registered General Practice Nurse</t>
         </is>
       </c>
       <c r="B22">
-        <v>23417.34</v>
+        <v>141837.28</v>
       </c>
       <c r="C22">
-        <v>18.2</v>
+        <v>81.11</v>
       </c>
       <c r="D22">
-        <v>42.43</v>
+        <v>184.62</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>18.44</v>
       </c>
       <c r="F22">
-        <v>425.63</v>
+        <v>2839.88</v>
       </c>
       <c r="G22">
-        <v>916</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Podiatrist</t>
+          <t>Registered Nurse</t>
         </is>
       </c>
       <c r="B23">
-        <v>33087</v>
+        <v>405048</v>
       </c>
       <c r="C23">
-        <v>320.12</v>
+        <v>104.1</v>
       </c>
       <c r="D23">
-        <v>303.7</v>
+        <v>245.03</v>
       </c>
       <c r="E23">
-        <v>20.51</v>
+        <v>21.01</v>
       </c>
       <c r="F23">
-        <v>1750.35</v>
+        <v>6136.2</v>
       </c>
       <c r="G23">
-        <v>61</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Professional Behavioral Health Counselor</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B24">
-        <v>14719</v>
+        <v>308</v>
       </c>
       <c r="C24">
-        <v>302.37</v>
+        <v>155.17</v>
       </c>
       <c r="D24">
-        <v>405.47</v>
+        <v>84.36</v>
       </c>
       <c r="E24">
-        <v>20.51</v>
+        <v>72.39</v>
       </c>
       <c r="F24">
-        <v>1887.29</v>
+        <v>191.7</v>
       </c>
       <c r="G24">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Radiography Technologist</t>
+          <t>Specialist</t>
         </is>
       </c>
       <c r="B25">
-        <v>103.72</v>
+        <v>17333.39</v>
       </c>
       <c r="C25">
-        <v>8.390000000000001</v>
+        <v>63.14</v>
       </c>
       <c r="D25">
-        <v>4.64</v>
+        <v>119.82</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>14.63</v>
       </c>
       <c r="F25">
-        <v>13.87</v>
+        <v>1011.43</v>
       </c>
       <c r="G25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Registered Community Health Nurse</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>1387977.9</v>
-      </c>
-      <c r="C26">
-        <v>244.13</v>
-      </c>
-      <c r="D26">
-        <v>599.21</v>
-      </c>
-      <c r="E26">
-        <v>9.6</v>
-      </c>
-      <c r="F26">
-        <v>14241.9</v>
-      </c>
-      <c r="G26">
-        <v>3731</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Registered Dietitian</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>14196</v>
-      </c>
-      <c r="C27">
-        <v>170.98</v>
-      </c>
-      <c r="D27">
-        <v>687.95</v>
-      </c>
-      <c r="E27">
-        <v>19.51</v>
-      </c>
-      <c r="F27">
-        <v>4885.88</v>
-      </c>
-      <c r="G27">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Registered General Practice Nurse</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>1387115.52</v>
-      </c>
-      <c r="C28">
-        <v>793.2</v>
-      </c>
-      <c r="D28">
-        <v>1718.99</v>
-      </c>
-      <c r="E28">
-        <v>36.89</v>
-      </c>
-      <c r="F28">
-        <v>23770.81</v>
-      </c>
-      <c r="G28">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Registered Nurse</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>2028936</v>
-      </c>
-      <c r="C29">
-        <v>521.45</v>
-      </c>
-      <c r="D29">
-        <v>934.38</v>
-      </c>
-      <c r="E29">
-        <v>21.01</v>
-      </c>
-      <c r="F29">
-        <v>13976.9</v>
-      </c>
-      <c r="G29">
-        <v>2502</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Registered Record Administrator</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>414374.55</v>
-      </c>
-      <c r="C30">
-        <v>21.24</v>
-      </c>
-      <c r="D30">
-        <v>44.56</v>
-      </c>
-      <c r="E30">
-        <v>0.64</v>
-      </c>
-      <c r="F30">
-        <v>661.14</v>
-      </c>
-      <c r="G30">
-        <v>14045</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>704</v>
-      </c>
-      <c r="C31">
-        <v>354.67</v>
-      </c>
-      <c r="D31">
-        <v>287.7</v>
-      </c>
-      <c r="E31">
-        <v>72.39</v>
-      </c>
-      <c r="F31">
-        <v>479.25</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Specialist</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>67521.3</v>
-      </c>
-      <c r="C32">
-        <v>245.96</v>
-      </c>
-      <c r="D32">
-        <v>395.04</v>
-      </c>
-      <c r="E32">
-        <v>14.63</v>
-      </c>
-      <c r="F32">
-        <v>2669.06</v>
-      </c>
-      <c r="G32">
         <v>183</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Student</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>919.03</v>
-      </c>
-      <c r="C33">
-        <v>2.98</v>
-      </c>
-      <c r="D33">
-        <v>10.95</v>
-      </c>
-      <c r="E33">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="F33">
-        <v>108.62</v>
-      </c>
-      <c r="G33">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Surgical Physician Assistant</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>1539.49</v>
-      </c>
-      <c r="C34">
-        <v>6.84</v>
-      </c>
-      <c r="D34">
-        <v>11.6</v>
-      </c>
-      <c r="E34">
-        <v>0.48</v>
-      </c>
-      <c r="F34">
-        <v>80.81999999999999</v>
-      </c>
-      <c r="G34">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -2116,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2159,125 +1666,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>2858338.71</v>
+        <v>16682022</v>
       </c>
       <c r="C2">
-        <v>99.59</v>
+        <v>570.11</v>
       </c>
       <c r="D2">
-        <v>193.06</v>
+        <v>615.84</v>
       </c>
       <c r="E2">
-        <v>0.64</v>
+        <v>21.01</v>
       </c>
       <c r="F2">
-        <v>4937.01</v>
+        <v>9557.690000000001</v>
       </c>
       <c r="G2">
-        <v>21325</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B3">
-        <v>43187508</v>
+        <v>1192853.87</v>
       </c>
       <c r="C3">
-        <v>1481.79</v>
+        <v>84.59</v>
       </c>
       <c r="D3">
-        <v>1823.64</v>
+        <v>189.85</v>
       </c>
       <c r="E3">
-        <v>21.01</v>
+        <v>9.6</v>
       </c>
       <c r="F3">
-        <v>32699.49</v>
+        <v>6136.2</v>
       </c>
       <c r="G3">
-        <v>21774</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="B4">
-        <v>15169330.1</v>
+        <v>1524367.08</v>
       </c>
       <c r="C4">
-        <v>645.67</v>
+        <v>122.12</v>
       </c>
       <c r="D4">
-        <v>1186.83</v>
+        <v>241.63</v>
       </c>
       <c r="E4">
-        <v>9.6</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>26899.89</v>
+        <v>2457.58</v>
       </c>
       <c r="G4">
-        <v>15613</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Uncategorised</t>
         </is>
       </c>
       <c r="B5">
-        <v>3692413.82</v>
+        <v>1531076.28</v>
       </c>
       <c r="C5">
-        <v>171.15</v>
+        <v>129.54</v>
       </c>
       <c r="D5">
-        <v>534.72</v>
+        <v>250.23</v>
       </c>
       <c r="E5">
-        <v>0.48</v>
+        <v>24.71</v>
       </c>
       <c r="F5">
-        <v>9143.24</v>
+        <v>3519.23</v>
       </c>
       <c r="G5">
-        <v>14899</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Uncategorised</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>4332255.54</v>
-      </c>
-      <c r="C6">
-        <v>366.54</v>
-      </c>
-      <c r="D6">
-        <v>817.64</v>
-      </c>
-      <c r="E6">
-        <v>24.71</v>
-      </c>
-      <c r="F6">
-        <v>20722.26</v>
-      </c>
-      <c r="G6">
         <v>7891</v>
       </c>
     </row>
@@ -2288,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2331,51 +1813,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>2879093.27</v>
+        <v>16682022</v>
       </c>
       <c r="C2">
-        <v>99.52</v>
+        <v>570.11</v>
       </c>
       <c r="D2">
-        <v>194.09</v>
+        <v>615.84</v>
       </c>
       <c r="E2">
-        <v>0.64</v>
+        <v>21.01</v>
       </c>
       <c r="F2">
-        <v>4937.01</v>
+        <v>9557.690000000001</v>
       </c>
       <c r="G2">
-        <v>21822</v>
+        <v>21900</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B3">
-        <v>43187508</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1481.79</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1823.64</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21.01</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>32699.49</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>21774</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4">
@@ -2385,22 +1867,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>15169330.1</v>
+        <v>1192853.87</v>
       </c>
       <c r="C4">
-        <v>645.67</v>
+        <v>84.59</v>
       </c>
       <c r="D4">
-        <v>1186.83</v>
+        <v>189.85</v>
       </c>
       <c r="E4">
         <v>9.6</v>
       </c>
       <c r="F4">
-        <v>26899.89</v>
+        <v>6136.2</v>
       </c>
       <c r="G4">
-        <v>15613</v>
+        <v>9362</v>
       </c>
     </row>
     <row r="5">
@@ -2410,22 +1892,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>3692413.82</v>
+        <v>1524367.08</v>
       </c>
       <c r="C5">
-        <v>171.15</v>
+        <v>122.12</v>
       </c>
       <c r="D5">
-        <v>534.72</v>
+        <v>241.63</v>
       </c>
       <c r="E5">
-        <v>0.48</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>9143.24</v>
+        <v>2457.58</v>
       </c>
       <c r="G5">
-        <v>14899</v>
+        <v>8547</v>
       </c>
     </row>
     <row r="6">
@@ -2435,40 +1917,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>4332255.54</v>
+        <v>1531076.28</v>
       </c>
       <c r="C6">
-        <v>366.54</v>
+        <v>129.54</v>
       </c>
       <c r="D6">
-        <v>817.64</v>
+        <v>250.23</v>
       </c>
       <c r="E6">
         <v>24.71</v>
       </c>
       <c r="F6">
-        <v>20722.26</v>
+        <v>3519.23</v>
       </c>
       <c r="G6">
         <v>7891</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
       </c>
     </row>
   </sheetData>
